--- a/Practice Excel Sheets/Lesson 7-Sort Data in Excel/7-Excel-Sort in Excel.xlsx
+++ b/Practice Excel Sheets/Lesson 7-Sort Data in Excel/7-Excel-Sort in Excel.xlsx
@@ -1,26 +1,64 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30030"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CHANNELS\Satish Dhawale\Excel Beginners to Advance\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUVRAJ\Desktop\My Activities\GitHub\Excel\Practice Excel Sheets\Lesson 7-Sort Data in Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F72AE9-817C-4101-B505-09C3D53931EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C5A845-0F2E-48B8-B6F5-26C997001DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Employee Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Sorting" sheetId="2" r:id="rId2"/>
+    <sheet name="Fitering" sheetId="3" r:id="rId3"/>
+    <sheet name="Filter using list" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="95">
   <si>
     <t>Employee_ID</t>
   </si>
@@ -281,6 +319,30 @@
   </si>
   <si>
     <t>Prakash</t>
+  </si>
+  <si>
+    <t>Col no</t>
+  </si>
+  <si>
+    <t>sorting type</t>
+  </si>
+  <si>
+    <t>We can modify formula according to us and can apply sorting methods dynamically</t>
+  </si>
+  <si>
+    <t>filtred data of males</t>
+  </si>
+  <si>
+    <t>Filtering of data using list (data validation)</t>
+  </si>
+  <si>
+    <t>Departments</t>
+  </si>
+  <si>
+    <t>filtering by gender</t>
+  </si>
+  <si>
+    <t>filtering by department</t>
   </si>
 </sst>
 </file>
@@ -5089,4 +5151,9789 @@
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DFA70B1-9B76-4971-9EA6-C046A0E23CBA}">
+  <dimension ref="A1:Q101"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2" cm="1">
+        <f t="array" ref="A2:N101">_xlfn._xlws.SORT('Employee Data'!A2:N101,Q2,Q3)</f>
+        <v>21</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Amit</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Pillai</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="G2">
+        <v>79664</v>
+      </c>
+      <c r="H2">
+        <v>15932</v>
+      </c>
+      <c r="I2">
+        <v>7966</v>
+      </c>
+      <c r="J2">
+        <v>8826</v>
+      </c>
+      <c r="K2">
+        <v>112388</v>
+      </c>
+      <c r="L2">
+        <v>9559</v>
+      </c>
+      <c r="M2">
+        <v>11238</v>
+      </c>
+      <c r="N2">
+        <v>91591</v>
+      </c>
+      <c r="P2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>74</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Rahul</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Verma</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="G3">
+        <v>79526</v>
+      </c>
+      <c r="H3">
+        <v>15905</v>
+      </c>
+      <c r="I3">
+        <v>7952</v>
+      </c>
+      <c r="J3">
+        <v>6990</v>
+      </c>
+      <c r="K3">
+        <v>110373</v>
+      </c>
+      <c r="L3">
+        <v>9543</v>
+      </c>
+      <c r="M3">
+        <v>11037</v>
+      </c>
+      <c r="N3">
+        <v>89793</v>
+      </c>
+      <c r="P3" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>52</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Gaurav</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Desai</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G4">
+        <v>79232</v>
+      </c>
+      <c r="H4">
+        <v>15846</v>
+      </c>
+      <c r="I4">
+        <v>7923</v>
+      </c>
+      <c r="J4">
+        <v>7211</v>
+      </c>
+      <c r="K4">
+        <v>110212</v>
+      </c>
+      <c r="L4">
+        <v>9507</v>
+      </c>
+      <c r="M4">
+        <v>11021</v>
+      </c>
+      <c r="N4">
+        <v>89684</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>27</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Ramesh</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Gupta</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E5" t="str">
+        <v>IT</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="G5">
+        <v>78665</v>
+      </c>
+      <c r="H5">
+        <v>15733</v>
+      </c>
+      <c r="I5">
+        <v>7866</v>
+      </c>
+      <c r="J5">
+        <v>3924</v>
+      </c>
+      <c r="K5">
+        <v>106188</v>
+      </c>
+      <c r="L5">
+        <v>9439</v>
+      </c>
+      <c r="M5">
+        <v>10618</v>
+      </c>
+      <c r="N5">
+        <v>86131</v>
+      </c>
+      <c r="P5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>75</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Isha</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Sharma</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E6" t="str">
+        <v>HR</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G6">
+        <v>77565</v>
+      </c>
+      <c r="H6">
+        <v>15513</v>
+      </c>
+      <c r="I6">
+        <v>7756</v>
+      </c>
+      <c r="J6">
+        <v>8360</v>
+      </c>
+      <c r="K6">
+        <v>109194</v>
+      </c>
+      <c r="L6">
+        <v>9307</v>
+      </c>
+      <c r="M6">
+        <v>10919</v>
+      </c>
+      <c r="N6">
+        <v>88968</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>57</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Rekha</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Verma</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="G7">
+        <v>77187</v>
+      </c>
+      <c r="H7">
+        <v>15437</v>
+      </c>
+      <c r="I7">
+        <v>7718</v>
+      </c>
+      <c r="J7">
+        <v>9513</v>
+      </c>
+      <c r="K7">
+        <v>109855</v>
+      </c>
+      <c r="L7">
+        <v>9262</v>
+      </c>
+      <c r="M7">
+        <v>10985</v>
+      </c>
+      <c r="N7">
+        <v>89608</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>8</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Suresh</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Verma</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G8">
+        <v>75829</v>
+      </c>
+      <c r="H8">
+        <v>15165</v>
+      </c>
+      <c r="I8">
+        <v>7582</v>
+      </c>
+      <c r="J8">
+        <v>9631</v>
+      </c>
+      <c r="K8">
+        <v>108207</v>
+      </c>
+      <c r="L8">
+        <v>9099</v>
+      </c>
+      <c r="M8">
+        <v>10820</v>
+      </c>
+      <c r="N8">
+        <v>88288</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>17</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Shreya</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Patel</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E9" t="str">
+        <v>IT</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="G9">
+        <v>75759</v>
+      </c>
+      <c r="H9">
+        <v>15151</v>
+      </c>
+      <c r="I9">
+        <v>7575</v>
+      </c>
+      <c r="J9">
+        <v>7059</v>
+      </c>
+      <c r="K9">
+        <v>105544</v>
+      </c>
+      <c r="L9">
+        <v>9091</v>
+      </c>
+      <c r="M9">
+        <v>10554</v>
+      </c>
+      <c r="N9">
+        <v>85899</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>93</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Vivek</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Naidu</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G10">
+        <v>75458</v>
+      </c>
+      <c r="H10">
+        <v>15091</v>
+      </c>
+      <c r="I10">
+        <v>7545</v>
+      </c>
+      <c r="J10">
+        <v>2729</v>
+      </c>
+      <c r="K10">
+        <v>100823</v>
+      </c>
+      <c r="L10">
+        <v>9054</v>
+      </c>
+      <c r="M10">
+        <v>10082</v>
+      </c>
+      <c r="N10">
+        <v>81687</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>14</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Ramesh</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Kulkarni</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G11">
+        <v>74084</v>
+      </c>
+      <c r="H11">
+        <v>14816</v>
+      </c>
+      <c r="I11">
+        <v>7408</v>
+      </c>
+      <c r="J11">
+        <v>3612</v>
+      </c>
+      <c r="K11">
+        <v>99920</v>
+      </c>
+      <c r="L11">
+        <v>8890</v>
+      </c>
+      <c r="M11">
+        <v>9992</v>
+      </c>
+      <c r="N11">
+        <v>81038</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>97</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Payal</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Naidu</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="G12">
+        <v>73201</v>
+      </c>
+      <c r="H12">
+        <v>14640</v>
+      </c>
+      <c r="I12">
+        <v>7320</v>
+      </c>
+      <c r="J12">
+        <v>9948</v>
+      </c>
+      <c r="K12">
+        <v>105109</v>
+      </c>
+      <c r="L12">
+        <v>8784</v>
+      </c>
+      <c r="M12">
+        <v>10510</v>
+      </c>
+      <c r="N12">
+        <v>85815</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>70</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Sunita</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Kumar</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E13" t="str">
+        <v>HR</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="G13">
+        <v>72192</v>
+      </c>
+      <c r="H13">
+        <v>14438</v>
+      </c>
+      <c r="I13">
+        <v>7219</v>
+      </c>
+      <c r="J13">
+        <v>6505</v>
+      </c>
+      <c r="K13">
+        <v>100354</v>
+      </c>
+      <c r="L13">
+        <v>8663</v>
+      </c>
+      <c r="M13">
+        <v>10035</v>
+      </c>
+      <c r="N13">
+        <v>81656</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>41</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Arjun</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Nair</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E14" t="str">
+        <v>IT</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="G14">
+        <v>72163</v>
+      </c>
+      <c r="H14">
+        <v>14432</v>
+      </c>
+      <c r="I14">
+        <v>7216</v>
+      </c>
+      <c r="J14">
+        <v>6978</v>
+      </c>
+      <c r="K14">
+        <v>100789</v>
+      </c>
+      <c r="L14">
+        <v>8659</v>
+      </c>
+      <c r="M14">
+        <v>10078</v>
+      </c>
+      <c r="N14">
+        <v>82052</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>49</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Ramesh</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Singh</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G15">
+        <v>71786</v>
+      </c>
+      <c r="H15">
+        <v>14357</v>
+      </c>
+      <c r="I15">
+        <v>7178</v>
+      </c>
+      <c r="J15">
+        <v>3357</v>
+      </c>
+      <c r="K15">
+        <v>96678</v>
+      </c>
+      <c r="L15">
+        <v>8614</v>
+      </c>
+      <c r="M15">
+        <v>9667</v>
+      </c>
+      <c r="N15">
+        <v>78397</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>73</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Deepak</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Gupta</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="G16">
+        <v>70564</v>
+      </c>
+      <c r="H16">
+        <v>14112</v>
+      </c>
+      <c r="I16">
+        <v>7056</v>
+      </c>
+      <c r="J16">
+        <v>9182</v>
+      </c>
+      <c r="K16">
+        <v>100914</v>
+      </c>
+      <c r="L16">
+        <v>8467</v>
+      </c>
+      <c r="M16">
+        <v>10091</v>
+      </c>
+      <c r="N16">
+        <v>82356</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>18</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Aarti</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Sharma</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E17" t="str">
+        <v>HR</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G17">
+        <v>70505</v>
+      </c>
+      <c r="H17">
+        <v>14101</v>
+      </c>
+      <c r="I17">
+        <v>7050</v>
+      </c>
+      <c r="J17">
+        <v>3430</v>
+      </c>
+      <c r="K17">
+        <v>95086</v>
+      </c>
+      <c r="L17">
+        <v>8460</v>
+      </c>
+      <c r="M17">
+        <v>9508</v>
+      </c>
+      <c r="N17">
+        <v>77118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>30</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Rohit</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Singh</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G18">
+        <v>70224</v>
+      </c>
+      <c r="H18">
+        <v>14044</v>
+      </c>
+      <c r="I18">
+        <v>7022</v>
+      </c>
+      <c r="J18">
+        <v>2902</v>
+      </c>
+      <c r="K18">
+        <v>94192</v>
+      </c>
+      <c r="L18">
+        <v>8426</v>
+      </c>
+      <c r="M18">
+        <v>9419</v>
+      </c>
+      <c r="N18">
+        <v>76347</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>2</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Swati</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Mishra</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="G19">
+        <v>70205</v>
+      </c>
+      <c r="H19">
+        <v>14041</v>
+      </c>
+      <c r="I19">
+        <v>7020</v>
+      </c>
+      <c r="J19">
+        <v>5973</v>
+      </c>
+      <c r="K19">
+        <v>97239</v>
+      </c>
+      <c r="L19">
+        <v>8424</v>
+      </c>
+      <c r="M19">
+        <v>9723</v>
+      </c>
+      <c r="N19">
+        <v>79092</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>5</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Vivek</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Kumar</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G20">
+        <v>68374</v>
+      </c>
+      <c r="H20">
+        <v>13674</v>
+      </c>
+      <c r="I20">
+        <v>6837</v>
+      </c>
+      <c r="J20">
+        <v>7208</v>
+      </c>
+      <c r="K20">
+        <v>96093</v>
+      </c>
+      <c r="L20">
+        <v>8204</v>
+      </c>
+      <c r="M20">
+        <v>9609</v>
+      </c>
+      <c r="N20">
+        <v>78280</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Nisha</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Bose</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="G21">
+        <v>68167</v>
+      </c>
+      <c r="H21">
+        <v>13633</v>
+      </c>
+      <c r="I21">
+        <v>6816</v>
+      </c>
+      <c r="J21">
+        <v>6534</v>
+      </c>
+      <c r="K21">
+        <v>95150</v>
+      </c>
+      <c r="L21">
+        <v>8180</v>
+      </c>
+      <c r="M21">
+        <v>9515</v>
+      </c>
+      <c r="N21">
+        <v>77455</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>23</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Pooja</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Pillai</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="G22">
+        <v>67845</v>
+      </c>
+      <c r="H22">
+        <v>13569</v>
+      </c>
+      <c r="I22">
+        <v>6784</v>
+      </c>
+      <c r="J22">
+        <v>5776</v>
+      </c>
+      <c r="K22">
+        <v>93974</v>
+      </c>
+      <c r="L22">
+        <v>8141</v>
+      </c>
+      <c r="M22">
+        <v>9397</v>
+      </c>
+      <c r="N22">
+        <v>76436</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>10</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Rahul</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Mishra</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="G23">
+        <v>67435</v>
+      </c>
+      <c r="H23">
+        <v>13487</v>
+      </c>
+      <c r="I23">
+        <v>6743</v>
+      </c>
+      <c r="J23">
+        <v>9563</v>
+      </c>
+      <c r="K23">
+        <v>97228</v>
+      </c>
+      <c r="L23">
+        <v>8092</v>
+      </c>
+      <c r="M23">
+        <v>9722</v>
+      </c>
+      <c r="N23">
+        <v>79414</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>63</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Pooja</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Chatterjee</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G24">
+        <v>66958</v>
+      </c>
+      <c r="H24">
+        <v>13391</v>
+      </c>
+      <c r="I24">
+        <v>6695</v>
+      </c>
+      <c r="J24">
+        <v>9327</v>
+      </c>
+      <c r="K24">
+        <v>96371</v>
+      </c>
+      <c r="L24">
+        <v>8034</v>
+      </c>
+      <c r="M24">
+        <v>9637</v>
+      </c>
+      <c r="N24">
+        <v>78700</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>95</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Isha</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Singh</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G25">
+        <v>66819</v>
+      </c>
+      <c r="H25">
+        <v>13363</v>
+      </c>
+      <c r="I25">
+        <v>6681</v>
+      </c>
+      <c r="J25">
+        <v>5844</v>
+      </c>
+      <c r="K25">
+        <v>92707</v>
+      </c>
+      <c r="L25">
+        <v>8018</v>
+      </c>
+      <c r="M25">
+        <v>9270</v>
+      </c>
+      <c r="N25">
+        <v>75419</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>83</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Manish</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Desai</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="G26">
+        <v>65463</v>
+      </c>
+      <c r="H26">
+        <v>13092</v>
+      </c>
+      <c r="I26">
+        <v>6546</v>
+      </c>
+      <c r="J26">
+        <v>6107</v>
+      </c>
+      <c r="K26">
+        <v>91208</v>
+      </c>
+      <c r="L26">
+        <v>7855</v>
+      </c>
+      <c r="M26">
+        <v>9120</v>
+      </c>
+      <c r="N26">
+        <v>74233</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>87</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Yash</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Reddy</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G27">
+        <v>65347</v>
+      </c>
+      <c r="H27">
+        <v>13069</v>
+      </c>
+      <c r="I27">
+        <v>6534</v>
+      </c>
+      <c r="J27">
+        <v>7333</v>
+      </c>
+      <c r="K27">
+        <v>92283</v>
+      </c>
+      <c r="L27">
+        <v>7841</v>
+      </c>
+      <c r="M27">
+        <v>9228</v>
+      </c>
+      <c r="N27">
+        <v>75214</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>94</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Deepak</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Yadav</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E28" t="str">
+        <v>HR</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="G28">
+        <v>64799</v>
+      </c>
+      <c r="H28">
+        <v>12959</v>
+      </c>
+      <c r="I28">
+        <v>6479</v>
+      </c>
+      <c r="J28">
+        <v>9314</v>
+      </c>
+      <c r="K28">
+        <v>93551</v>
+      </c>
+      <c r="L28">
+        <v>7775</v>
+      </c>
+      <c r="M28">
+        <v>9355</v>
+      </c>
+      <c r="N28">
+        <v>76421</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>58</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Sunita</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Verma</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="G29">
+        <v>64622</v>
+      </c>
+      <c r="H29">
+        <v>12924</v>
+      </c>
+      <c r="I29">
+        <v>6462</v>
+      </c>
+      <c r="J29">
+        <v>3308</v>
+      </c>
+      <c r="K29">
+        <v>87316</v>
+      </c>
+      <c r="L29">
+        <v>7754</v>
+      </c>
+      <c r="M29">
+        <v>8731</v>
+      </c>
+      <c r="N29">
+        <v>70831</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Varun</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Iyer</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="G30">
+        <v>63476</v>
+      </c>
+      <c r="H30">
+        <v>12695</v>
+      </c>
+      <c r="I30">
+        <v>6347</v>
+      </c>
+      <c r="J30">
+        <v>4326</v>
+      </c>
+      <c r="K30">
+        <v>86844</v>
+      </c>
+      <c r="L30">
+        <v>7617</v>
+      </c>
+      <c r="M30">
+        <v>8684</v>
+      </c>
+      <c r="N30">
+        <v>70543</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>32</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Priya</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Chatterjee</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E31" t="str">
+        <v>IT</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G31">
+        <v>62716</v>
+      </c>
+      <c r="H31">
+        <v>12543</v>
+      </c>
+      <c r="I31">
+        <v>6271</v>
+      </c>
+      <c r="J31">
+        <v>6108</v>
+      </c>
+      <c r="K31">
+        <v>87638</v>
+      </c>
+      <c r="L31">
+        <v>7525</v>
+      </c>
+      <c r="M31">
+        <v>8763</v>
+      </c>
+      <c r="N31">
+        <v>71350</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>44</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Priya</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Singh</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="G32">
+        <v>62114</v>
+      </c>
+      <c r="H32">
+        <v>12422</v>
+      </c>
+      <c r="I32">
+        <v>6211</v>
+      </c>
+      <c r="J32">
+        <v>8503</v>
+      </c>
+      <c r="K32">
+        <v>89250</v>
+      </c>
+      <c r="L32">
+        <v>7453</v>
+      </c>
+      <c r="M32">
+        <v>8925</v>
+      </c>
+      <c r="N32">
+        <v>72872</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>3</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Sunita</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Naidu</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E33" t="str">
+        <v>HR</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G33">
+        <v>62004</v>
+      </c>
+      <c r="H33">
+        <v>12400</v>
+      </c>
+      <c r="I33">
+        <v>6200</v>
+      </c>
+      <c r="J33">
+        <v>3965</v>
+      </c>
+      <c r="K33">
+        <v>84569</v>
+      </c>
+      <c r="L33">
+        <v>7440</v>
+      </c>
+      <c r="M33">
+        <v>8456</v>
+      </c>
+      <c r="N33">
+        <v>68673</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>50</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Tanuja</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Bose</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G34">
+        <v>60843</v>
+      </c>
+      <c r="H34">
+        <v>12168</v>
+      </c>
+      <c r="I34">
+        <v>6084</v>
+      </c>
+      <c r="J34">
+        <v>4747</v>
+      </c>
+      <c r="K34">
+        <v>83842</v>
+      </c>
+      <c r="L34">
+        <v>7301</v>
+      </c>
+      <c r="M34">
+        <v>8384</v>
+      </c>
+      <c r="N34">
+        <v>68157</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>91</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Neha</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Chatterjee</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="G35">
+        <v>59553</v>
+      </c>
+      <c r="H35">
+        <v>11910</v>
+      </c>
+      <c r="I35">
+        <v>5955</v>
+      </c>
+      <c r="J35">
+        <v>5930</v>
+      </c>
+      <c r="K35">
+        <v>83348</v>
+      </c>
+      <c r="L35">
+        <v>7146</v>
+      </c>
+      <c r="M35">
+        <v>8334</v>
+      </c>
+      <c r="N35">
+        <v>67868</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>16</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Ramesh</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Pillai</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G36">
+        <v>59401</v>
+      </c>
+      <c r="H36">
+        <v>11880</v>
+      </c>
+      <c r="I36">
+        <v>5940</v>
+      </c>
+      <c r="J36">
+        <v>8652</v>
+      </c>
+      <c r="K36">
+        <v>85873</v>
+      </c>
+      <c r="L36">
+        <v>7128</v>
+      </c>
+      <c r="M36">
+        <v>8587</v>
+      </c>
+      <c r="N36">
+        <v>70158</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>48</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Shreya</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Joshi</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G37">
+        <v>59008</v>
+      </c>
+      <c r="H37">
+        <v>11801</v>
+      </c>
+      <c r="I37">
+        <v>5900</v>
+      </c>
+      <c r="J37">
+        <v>4141</v>
+      </c>
+      <c r="K37">
+        <v>80850</v>
+      </c>
+      <c r="L37">
+        <v>7080</v>
+      </c>
+      <c r="M37">
+        <v>8085</v>
+      </c>
+      <c r="N37">
+        <v>65685</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>25</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Sanjay</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Patel</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E38" t="str">
+        <v>IT</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G38">
+        <v>58962</v>
+      </c>
+      <c r="H38">
+        <v>11792</v>
+      </c>
+      <c r="I38">
+        <v>5896</v>
+      </c>
+      <c r="J38">
+        <v>6829</v>
+      </c>
+      <c r="K38">
+        <v>83479</v>
+      </c>
+      <c r="L38">
+        <v>7075</v>
+      </c>
+      <c r="M38">
+        <v>8347</v>
+      </c>
+      <c r="N38">
+        <v>68057</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>82</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Akash</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Joshi</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="G39">
+        <v>58807</v>
+      </c>
+      <c r="H39">
+        <v>11761</v>
+      </c>
+      <c r="I39">
+        <v>5880</v>
+      </c>
+      <c r="J39">
+        <v>6518</v>
+      </c>
+      <c r="K39">
+        <v>82966</v>
+      </c>
+      <c r="L39">
+        <v>7056</v>
+      </c>
+      <c r="M39">
+        <v>8296</v>
+      </c>
+      <c r="N39">
+        <v>67614</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>1</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Deepak</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Singh</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="G40">
+        <v>58591</v>
+      </c>
+      <c r="H40">
+        <v>11718</v>
+      </c>
+      <c r="I40">
+        <v>5859</v>
+      </c>
+      <c r="J40">
+        <v>3532</v>
+      </c>
+      <c r="K40">
+        <v>79700</v>
+      </c>
+      <c r="L40">
+        <v>7030</v>
+      </c>
+      <c r="M40">
+        <v>7970</v>
+      </c>
+      <c r="N40">
+        <v>64700</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>31</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Ramesh</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Patel</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="G41">
+        <v>57847</v>
+      </c>
+      <c r="H41">
+        <v>11569</v>
+      </c>
+      <c r="I41">
+        <v>5784</v>
+      </c>
+      <c r="J41">
+        <v>5757</v>
+      </c>
+      <c r="K41">
+        <v>80957</v>
+      </c>
+      <c r="L41">
+        <v>6941</v>
+      </c>
+      <c r="M41">
+        <v>8095</v>
+      </c>
+      <c r="N41">
+        <v>65921</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>69</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Sanjay</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Mishra</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="G42">
+        <v>57318</v>
+      </c>
+      <c r="H42">
+        <v>11463</v>
+      </c>
+      <c r="I42">
+        <v>5731</v>
+      </c>
+      <c r="J42">
+        <v>5077</v>
+      </c>
+      <c r="K42">
+        <v>79589</v>
+      </c>
+      <c r="L42">
+        <v>6878</v>
+      </c>
+      <c r="M42">
+        <v>7958</v>
+      </c>
+      <c r="N42">
+        <v>64753</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>88</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Pooja</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Nair</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="G43">
+        <v>57201</v>
+      </c>
+      <c r="H43">
+        <v>11440</v>
+      </c>
+      <c r="I43">
+        <v>5720</v>
+      </c>
+      <c r="J43">
+        <v>8967</v>
+      </c>
+      <c r="K43">
+        <v>83328</v>
+      </c>
+      <c r="L43">
+        <v>6864</v>
+      </c>
+      <c r="M43">
+        <v>8332</v>
+      </c>
+      <c r="N43">
+        <v>68132</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>22</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Rekha</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Iyer</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="G44">
+        <v>56954</v>
+      </c>
+      <c r="H44">
+        <v>11390</v>
+      </c>
+      <c r="I44">
+        <v>5695</v>
+      </c>
+      <c r="J44">
+        <v>3033</v>
+      </c>
+      <c r="K44">
+        <v>77072</v>
+      </c>
+      <c r="L44">
+        <v>6834</v>
+      </c>
+      <c r="M44">
+        <v>7707</v>
+      </c>
+      <c r="N44">
+        <v>62531</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>79</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Vikas</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Nair</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E45" t="str">
+        <v>IT</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="G45">
+        <v>55880</v>
+      </c>
+      <c r="H45">
+        <v>11176</v>
+      </c>
+      <c r="I45">
+        <v>5588</v>
+      </c>
+      <c r="J45">
+        <v>4176</v>
+      </c>
+      <c r="K45">
+        <v>76820</v>
+      </c>
+      <c r="L45">
+        <v>6705</v>
+      </c>
+      <c r="M45">
+        <v>7682</v>
+      </c>
+      <c r="N45">
+        <v>62433</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>72</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Divya</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Bose</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="G46">
+        <v>54929</v>
+      </c>
+      <c r="H46">
+        <v>10985</v>
+      </c>
+      <c r="I46">
+        <v>5492</v>
+      </c>
+      <c r="J46">
+        <v>4242</v>
+      </c>
+      <c r="K46">
+        <v>75648</v>
+      </c>
+      <c r="L46">
+        <v>6591</v>
+      </c>
+      <c r="M46">
+        <v>7564</v>
+      </c>
+      <c r="N46">
+        <v>61493</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>15</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Sneha</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Das</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G47">
+        <v>54644</v>
+      </c>
+      <c r="H47">
+        <v>10928</v>
+      </c>
+      <c r="I47">
+        <v>5464</v>
+      </c>
+      <c r="J47">
+        <v>2644</v>
+      </c>
+      <c r="K47">
+        <v>73680</v>
+      </c>
+      <c r="L47">
+        <v>6557</v>
+      </c>
+      <c r="M47">
+        <v>7368</v>
+      </c>
+      <c r="N47">
+        <v>59755</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>100</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Payal</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Yadav</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G48">
+        <v>54298</v>
+      </c>
+      <c r="H48">
+        <v>10859</v>
+      </c>
+      <c r="I48">
+        <v>5429</v>
+      </c>
+      <c r="J48">
+        <v>9879</v>
+      </c>
+      <c r="K48">
+        <v>80465</v>
+      </c>
+      <c r="L48">
+        <v>6515</v>
+      </c>
+      <c r="M48">
+        <v>8046</v>
+      </c>
+      <c r="N48">
+        <v>65904</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>45</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Gaurav</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Verma</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E49" t="str">
+        <v>HR</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G49">
+        <v>53871</v>
+      </c>
+      <c r="H49">
+        <v>10774</v>
+      </c>
+      <c r="I49">
+        <v>5387</v>
+      </c>
+      <c r="J49">
+        <v>9976</v>
+      </c>
+      <c r="K49">
+        <v>80008</v>
+      </c>
+      <c r="L49">
+        <v>6464</v>
+      </c>
+      <c r="M49">
+        <v>8000</v>
+      </c>
+      <c r="N49">
+        <v>65544</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>56</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Kavita</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Sharma</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="G50">
+        <v>53126</v>
+      </c>
+      <c r="H50">
+        <v>10625</v>
+      </c>
+      <c r="I50">
+        <v>5312</v>
+      </c>
+      <c r="J50">
+        <v>6479</v>
+      </c>
+      <c r="K50">
+        <v>75542</v>
+      </c>
+      <c r="L50">
+        <v>6375</v>
+      </c>
+      <c r="M50">
+        <v>7554</v>
+      </c>
+      <c r="N50">
+        <v>61613</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>78</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Ramesh</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Verma</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="G51">
+        <v>52061</v>
+      </c>
+      <c r="H51">
+        <v>10412</v>
+      </c>
+      <c r="I51">
+        <v>5206</v>
+      </c>
+      <c r="J51">
+        <v>6800</v>
+      </c>
+      <c r="K51">
+        <v>74479</v>
+      </c>
+      <c r="L51">
+        <v>6247</v>
+      </c>
+      <c r="M51">
+        <v>7447</v>
+      </c>
+      <c r="N51">
+        <v>60785</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>9</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Anjali</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Patel</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="G52">
+        <v>52037</v>
+      </c>
+      <c r="H52">
+        <v>10407</v>
+      </c>
+      <c r="I52">
+        <v>5203</v>
+      </c>
+      <c r="J52">
+        <v>4853</v>
+      </c>
+      <c r="K52">
+        <v>72500</v>
+      </c>
+      <c r="L52">
+        <v>6244</v>
+      </c>
+      <c r="M52">
+        <v>7250</v>
+      </c>
+      <c r="N52">
+        <v>59006</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>11</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Rashmi</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Mishra</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F53" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="G53">
+        <v>52011</v>
+      </c>
+      <c r="H53">
+        <v>10402</v>
+      </c>
+      <c r="I53">
+        <v>5201</v>
+      </c>
+      <c r="J53">
+        <v>4542</v>
+      </c>
+      <c r="K53">
+        <v>72156</v>
+      </c>
+      <c r="L53">
+        <v>6241</v>
+      </c>
+      <c r="M53">
+        <v>7215</v>
+      </c>
+      <c r="N53">
+        <v>58700</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>46</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Shreya</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Desai</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F54" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="G54">
+        <v>51805</v>
+      </c>
+      <c r="H54">
+        <v>10361</v>
+      </c>
+      <c r="I54">
+        <v>5180</v>
+      </c>
+      <c r="J54">
+        <v>8670</v>
+      </c>
+      <c r="K54">
+        <v>76016</v>
+      </c>
+      <c r="L54">
+        <v>6216</v>
+      </c>
+      <c r="M54">
+        <v>7601</v>
+      </c>
+      <c r="N54">
+        <v>62199</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>86</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Payal</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Joshi</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E55" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F55" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="G55">
+        <v>50437</v>
+      </c>
+      <c r="H55">
+        <v>10087</v>
+      </c>
+      <c r="I55">
+        <v>5043</v>
+      </c>
+      <c r="J55">
+        <v>5150</v>
+      </c>
+      <c r="K55">
+        <v>70717</v>
+      </c>
+      <c r="L55">
+        <v>6052</v>
+      </c>
+      <c r="M55">
+        <v>7071</v>
+      </c>
+      <c r="N55">
+        <v>57594</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>39</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Kavita</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Desai</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E56" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="F56" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="G56">
+        <v>50328</v>
+      </c>
+      <c r="H56">
+        <v>10065</v>
+      </c>
+      <c r="I56">
+        <v>5032</v>
+      </c>
+      <c r="J56">
+        <v>6720</v>
+      </c>
+      <c r="K56">
+        <v>72145</v>
+      </c>
+      <c r="L56">
+        <v>6039</v>
+      </c>
+      <c r="M56">
+        <v>7214</v>
+      </c>
+      <c r="N56">
+        <v>58892</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>34</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Isha</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Chatterjee</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E57" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="F57" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G57">
+        <v>49855</v>
+      </c>
+      <c r="H57">
+        <v>9971</v>
+      </c>
+      <c r="I57">
+        <v>4985</v>
+      </c>
+      <c r="J57">
+        <v>3415</v>
+      </c>
+      <c r="K57">
+        <v>68226</v>
+      </c>
+      <c r="L57">
+        <v>5982</v>
+      </c>
+      <c r="M57">
+        <v>6822</v>
+      </c>
+      <c r="N57">
+        <v>55422</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>92</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Isha</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Joshi</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E58" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="F58" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="G58">
+        <v>49760</v>
+      </c>
+      <c r="H58">
+        <v>9952</v>
+      </c>
+      <c r="I58">
+        <v>4976</v>
+      </c>
+      <c r="J58">
+        <v>8137</v>
+      </c>
+      <c r="K58">
+        <v>72825</v>
+      </c>
+      <c r="L58">
+        <v>5971</v>
+      </c>
+      <c r="M58">
+        <v>7282</v>
+      </c>
+      <c r="N58">
+        <v>59572</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>26</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Swati</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Bose</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E59" t="str">
+        <v>IT</v>
+      </c>
+      <c r="F59" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G59">
+        <v>48968</v>
+      </c>
+      <c r="H59">
+        <v>9793</v>
+      </c>
+      <c r="I59">
+        <v>4896</v>
+      </c>
+      <c r="J59">
+        <v>8204</v>
+      </c>
+      <c r="K59">
+        <v>71861</v>
+      </c>
+      <c r="L59">
+        <v>5876</v>
+      </c>
+      <c r="M59">
+        <v>7186</v>
+      </c>
+      <c r="N59">
+        <v>58799</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>12</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Karan</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Mehta</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E60" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F60" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G60">
+        <v>48524</v>
+      </c>
+      <c r="H60">
+        <v>9704</v>
+      </c>
+      <c r="I60">
+        <v>4852</v>
+      </c>
+      <c r="J60">
+        <v>2310</v>
+      </c>
+      <c r="K60">
+        <v>65390</v>
+      </c>
+      <c r="L60">
+        <v>5822</v>
+      </c>
+      <c r="M60">
+        <v>6539</v>
+      </c>
+      <c r="N60">
+        <v>53029</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>4</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Varun</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Joshi</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E61" t="str">
+        <v>HR</v>
+      </c>
+      <c r="F61" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="G61">
+        <v>48337</v>
+      </c>
+      <c r="H61">
+        <v>9667</v>
+      </c>
+      <c r="I61">
+        <v>4833</v>
+      </c>
+      <c r="J61">
+        <v>4065</v>
+      </c>
+      <c r="K61">
+        <v>66902</v>
+      </c>
+      <c r="L61">
+        <v>5800</v>
+      </c>
+      <c r="M61">
+        <v>6690</v>
+      </c>
+      <c r="N61">
+        <v>54412</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>36</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Amit</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Bose</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E62" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="F62" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="G62">
+        <v>47876</v>
+      </c>
+      <c r="H62">
+        <v>9575</v>
+      </c>
+      <c r="I62">
+        <v>4787</v>
+      </c>
+      <c r="J62">
+        <v>6335</v>
+      </c>
+      <c r="K62">
+        <v>68573</v>
+      </c>
+      <c r="L62">
+        <v>5745</v>
+      </c>
+      <c r="M62">
+        <v>6857</v>
+      </c>
+      <c r="N62">
+        <v>55971</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>90</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Nikhil</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Naidu</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E63" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="F63" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G63">
+        <v>47602</v>
+      </c>
+      <c r="H63">
+        <v>9520</v>
+      </c>
+      <c r="I63">
+        <v>4760</v>
+      </c>
+      <c r="J63">
+        <v>3250</v>
+      </c>
+      <c r="K63">
+        <v>65132</v>
+      </c>
+      <c r="L63">
+        <v>5712</v>
+      </c>
+      <c r="M63">
+        <v>6513</v>
+      </c>
+      <c r="N63">
+        <v>52907</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>28</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Ramesh</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Yadav</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E64" t="str">
+        <v>HR</v>
+      </c>
+      <c r="F64" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="G64">
+        <v>47308</v>
+      </c>
+      <c r="H64">
+        <v>9461</v>
+      </c>
+      <c r="I64">
+        <v>4730</v>
+      </c>
+      <c r="J64">
+        <v>8299</v>
+      </c>
+      <c r="K64">
+        <v>69798</v>
+      </c>
+      <c r="L64">
+        <v>5676</v>
+      </c>
+      <c r="M64">
+        <v>6979</v>
+      </c>
+      <c r="N64">
+        <v>57143</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>37</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Suresh</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Nair</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E65" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F65" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="G65">
+        <v>45653</v>
+      </c>
+      <c r="H65">
+        <v>9130</v>
+      </c>
+      <c r="I65">
+        <v>4565</v>
+      </c>
+      <c r="J65">
+        <v>7327</v>
+      </c>
+      <c r="K65">
+        <v>66675</v>
+      </c>
+      <c r="L65">
+        <v>5478</v>
+      </c>
+      <c r="M65">
+        <v>6667</v>
+      </c>
+      <c r="N65">
+        <v>54530</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>35</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Rashmi</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Naidu</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E66" t="str">
+        <v>HR</v>
+      </c>
+      <c r="F66" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="G66">
+        <v>44961</v>
+      </c>
+      <c r="H66">
+        <v>8992</v>
+      </c>
+      <c r="I66">
+        <v>4496</v>
+      </c>
+      <c r="J66">
+        <v>2327</v>
+      </c>
+      <c r="K66">
+        <v>60776</v>
+      </c>
+      <c r="L66">
+        <v>5395</v>
+      </c>
+      <c r="M66">
+        <v>6077</v>
+      </c>
+      <c r="N66">
+        <v>49304</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>96</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Priya</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Joshi</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E67" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="F67" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="G67">
+        <v>44954</v>
+      </c>
+      <c r="H67">
+        <v>8990</v>
+      </c>
+      <c r="I67">
+        <v>4495</v>
+      </c>
+      <c r="J67">
+        <v>2259</v>
+      </c>
+      <c r="K67">
+        <v>60698</v>
+      </c>
+      <c r="L67">
+        <v>5394</v>
+      </c>
+      <c r="M67">
+        <v>6069</v>
+      </c>
+      <c r="N67">
+        <v>49235</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>80</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Komal</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Sharma</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E68" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F68" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G68">
+        <v>44871</v>
+      </c>
+      <c r="H68">
+        <v>8974</v>
+      </c>
+      <c r="I68">
+        <v>4487</v>
+      </c>
+      <c r="J68">
+        <v>3543</v>
+      </c>
+      <c r="K68">
+        <v>61875</v>
+      </c>
+      <c r="L68">
+        <v>5384</v>
+      </c>
+      <c r="M68">
+        <v>6187</v>
+      </c>
+      <c r="N68">
+        <v>50304</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>20</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Manish</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Gupta</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E69" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="F69" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G69">
+        <v>44462</v>
+      </c>
+      <c r="H69">
+        <v>8892</v>
+      </c>
+      <c r="I69">
+        <v>4446</v>
+      </c>
+      <c r="J69">
+        <v>3086</v>
+      </c>
+      <c r="K69">
+        <v>60886</v>
+      </c>
+      <c r="L69">
+        <v>5335</v>
+      </c>
+      <c r="M69">
+        <v>6088</v>
+      </c>
+      <c r="N69">
+        <v>49463</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>84</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Anil</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Kulkarni</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E70" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F70" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G70">
+        <v>44075</v>
+      </c>
+      <c r="H70">
+        <v>8815</v>
+      </c>
+      <c r="I70">
+        <v>4407</v>
+      </c>
+      <c r="J70">
+        <v>9661</v>
+      </c>
+      <c r="K70">
+        <v>66958</v>
+      </c>
+      <c r="L70">
+        <v>5289</v>
+      </c>
+      <c r="M70">
+        <v>6695</v>
+      </c>
+      <c r="N70">
+        <v>54974</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>99</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Prakash</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Iyer</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E71" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="F71" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="G71">
+        <v>41685</v>
+      </c>
+      <c r="H71">
+        <v>8337</v>
+      </c>
+      <c r="I71">
+        <v>4168</v>
+      </c>
+      <c r="J71">
+        <v>9202</v>
+      </c>
+      <c r="K71">
+        <v>63392</v>
+      </c>
+      <c r="L71">
+        <v>5002</v>
+      </c>
+      <c r="M71">
+        <v>6339</v>
+      </c>
+      <c r="N71">
+        <v>52051</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>54</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Nikhil</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Verma</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E72" t="str">
+        <v>HR</v>
+      </c>
+      <c r="F72" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G72">
+        <v>40881</v>
+      </c>
+      <c r="H72">
+        <v>8176</v>
+      </c>
+      <c r="I72">
+        <v>4088</v>
+      </c>
+      <c r="J72">
+        <v>3607</v>
+      </c>
+      <c r="K72">
+        <v>56752</v>
+      </c>
+      <c r="L72">
+        <v>4905</v>
+      </c>
+      <c r="M72">
+        <v>5675</v>
+      </c>
+      <c r="N72">
+        <v>46172</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>43</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Anjali</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Singh</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E73" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="F73" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="G73">
+        <v>40221</v>
+      </c>
+      <c r="H73">
+        <v>8044</v>
+      </c>
+      <c r="I73">
+        <v>4022</v>
+      </c>
+      <c r="J73">
+        <v>6861</v>
+      </c>
+      <c r="K73">
+        <v>59148</v>
+      </c>
+      <c r="L73">
+        <v>4826</v>
+      </c>
+      <c r="M73">
+        <v>5914</v>
+      </c>
+      <c r="N73">
+        <v>48408</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>81</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Priya</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Gupta</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E74" t="str">
+        <v>IT</v>
+      </c>
+      <c r="F74" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="G74">
+        <v>37428</v>
+      </c>
+      <c r="H74">
+        <v>7485</v>
+      </c>
+      <c r="I74">
+        <v>3742</v>
+      </c>
+      <c r="J74">
+        <v>8568</v>
+      </c>
+      <c r="K74">
+        <v>57223</v>
+      </c>
+      <c r="L74">
+        <v>4491</v>
+      </c>
+      <c r="M74">
+        <v>5722</v>
+      </c>
+      <c r="N74">
+        <v>47010</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>66</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Vikas</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Joshi</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E75" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F75" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="G75">
+        <v>36378</v>
+      </c>
+      <c r="H75">
+        <v>7275</v>
+      </c>
+      <c r="I75">
+        <v>3637</v>
+      </c>
+      <c r="J75">
+        <v>5600</v>
+      </c>
+      <c r="K75">
+        <v>52890</v>
+      </c>
+      <c r="L75">
+        <v>4365</v>
+      </c>
+      <c r="M75">
+        <v>5289</v>
+      </c>
+      <c r="N75">
+        <v>43236</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>53</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Meena</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Mehta</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E76" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="F76" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G76">
+        <v>35096</v>
+      </c>
+      <c r="H76">
+        <v>7019</v>
+      </c>
+      <c r="I76">
+        <v>3509</v>
+      </c>
+      <c r="J76">
+        <v>8514</v>
+      </c>
+      <c r="K76">
+        <v>54138</v>
+      </c>
+      <c r="L76">
+        <v>4211</v>
+      </c>
+      <c r="M76">
+        <v>5413</v>
+      </c>
+      <c r="N76">
+        <v>44514</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>61</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Aarti</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Patel</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E77" t="str">
+        <v>HR</v>
+      </c>
+      <c r="F77" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="G77">
+        <v>34491</v>
+      </c>
+      <c r="H77">
+        <v>6898</v>
+      </c>
+      <c r="I77">
+        <v>3449</v>
+      </c>
+      <c r="J77">
+        <v>7675</v>
+      </c>
+      <c r="K77">
+        <v>52513</v>
+      </c>
+      <c r="L77">
+        <v>4138</v>
+      </c>
+      <c r="M77">
+        <v>5251</v>
+      </c>
+      <c r="N77">
+        <v>43124</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>33</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Deepak</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Iyer</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E78" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="F78" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="G78">
+        <v>34427</v>
+      </c>
+      <c r="H78">
+        <v>6885</v>
+      </c>
+      <c r="I78">
+        <v>3442</v>
+      </c>
+      <c r="J78">
+        <v>5668</v>
+      </c>
+      <c r="K78">
+        <v>50422</v>
+      </c>
+      <c r="L78">
+        <v>4131</v>
+      </c>
+      <c r="M78">
+        <v>5042</v>
+      </c>
+      <c r="N78">
+        <v>41249</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>77</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Rahul</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Iyer</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E79" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="F79" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="G79">
+        <v>34264</v>
+      </c>
+      <c r="H79">
+        <v>6852</v>
+      </c>
+      <c r="I79">
+        <v>3426</v>
+      </c>
+      <c r="J79">
+        <v>9643</v>
+      </c>
+      <c r="K79">
+        <v>54185</v>
+      </c>
+      <c r="L79">
+        <v>4111</v>
+      </c>
+      <c r="M79">
+        <v>5418</v>
+      </c>
+      <c r="N79">
+        <v>44656</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>60</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Nikhil</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Mishra</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E80" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F80" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="G80">
+        <v>33947</v>
+      </c>
+      <c r="H80">
+        <v>6789</v>
+      </c>
+      <c r="I80">
+        <v>3394</v>
+      </c>
+      <c r="J80">
+        <v>3524</v>
+      </c>
+      <c r="K80">
+        <v>47654</v>
+      </c>
+      <c r="L80">
+        <v>4073</v>
+      </c>
+      <c r="M80">
+        <v>4765</v>
+      </c>
+      <c r="N80">
+        <v>38816</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>47</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Harish</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Verma</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E81" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="F81" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="G81">
+        <v>32824</v>
+      </c>
+      <c r="H81">
+        <v>6564</v>
+      </c>
+      <c r="I81">
+        <v>3282</v>
+      </c>
+      <c r="J81">
+        <v>9464</v>
+      </c>
+      <c r="K81">
+        <v>52134</v>
+      </c>
+      <c r="L81">
+        <v>3938</v>
+      </c>
+      <c r="M81">
+        <v>5213</v>
+      </c>
+      <c r="N81">
+        <v>42983</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>42</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Harish</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Reddy</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E82" t="str">
+        <v>IT</v>
+      </c>
+      <c r="F82" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G82">
+        <v>29984</v>
+      </c>
+      <c r="H82">
+        <v>5996</v>
+      </c>
+      <c r="I82">
+        <v>2998</v>
+      </c>
+      <c r="J82">
+        <v>2533</v>
+      </c>
+      <c r="K82">
+        <v>41511</v>
+      </c>
+      <c r="L82">
+        <v>3598</v>
+      </c>
+      <c r="M82">
+        <v>4151</v>
+      </c>
+      <c r="N82">
+        <v>33762</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>7</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Arjun</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Sharma</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E83" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="F83" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G83">
+        <v>29593</v>
+      </c>
+      <c r="H83">
+        <v>5918</v>
+      </c>
+      <c r="I83">
+        <v>2959</v>
+      </c>
+      <c r="J83">
+        <v>9188</v>
+      </c>
+      <c r="K83">
+        <v>47658</v>
+      </c>
+      <c r="L83">
+        <v>3551</v>
+      </c>
+      <c r="M83">
+        <v>4765</v>
+      </c>
+      <c r="N83">
+        <v>39342</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>65</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Isha</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Nair</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E84" t="str">
+        <v>HR</v>
+      </c>
+      <c r="F84" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="G84">
+        <v>29391</v>
+      </c>
+      <c r="H84">
+        <v>5878</v>
+      </c>
+      <c r="I84">
+        <v>2939</v>
+      </c>
+      <c r="J84">
+        <v>9277</v>
+      </c>
+      <c r="K84">
+        <v>47485</v>
+      </c>
+      <c r="L84">
+        <v>3526</v>
+      </c>
+      <c r="M84">
+        <v>4748</v>
+      </c>
+      <c r="N84">
+        <v>39211</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>6</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Arjun</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Kulkarni</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E85" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F85" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G85">
+        <v>29057</v>
+      </c>
+      <c r="H85">
+        <v>5811</v>
+      </c>
+      <c r="I85">
+        <v>2905</v>
+      </c>
+      <c r="J85">
+        <v>4753</v>
+      </c>
+      <c r="K85">
+        <v>42526</v>
+      </c>
+      <c r="L85">
+        <v>3486</v>
+      </c>
+      <c r="M85">
+        <v>4252</v>
+      </c>
+      <c r="N85">
+        <v>34788</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>67</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Harish</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Das</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E86" t="str">
+        <v>IT</v>
+      </c>
+      <c r="F86" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G86">
+        <v>26916</v>
+      </c>
+      <c r="H86">
+        <v>5383</v>
+      </c>
+      <c r="I86">
+        <v>2691</v>
+      </c>
+      <c r="J86">
+        <v>5457</v>
+      </c>
+      <c r="K86">
+        <v>40447</v>
+      </c>
+      <c r="L86">
+        <v>3229</v>
+      </c>
+      <c r="M86">
+        <v>4044</v>
+      </c>
+      <c r="N86">
+        <v>33174</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>76</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Karan</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Patel</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E87" t="str">
+        <v>HR</v>
+      </c>
+      <c r="F87" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="G87">
+        <v>25887</v>
+      </c>
+      <c r="H87">
+        <v>5177</v>
+      </c>
+      <c r="I87">
+        <v>2588</v>
+      </c>
+      <c r="J87">
+        <v>9023</v>
+      </c>
+      <c r="K87">
+        <v>42675</v>
+      </c>
+      <c r="L87">
+        <v>3106</v>
+      </c>
+      <c r="M87">
+        <v>4267</v>
+      </c>
+      <c r="N87">
+        <v>35302</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>59</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Aarti</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Naidu</v>
+      </c>
+      <c r="D88" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E88" t="str">
+        <v>IT</v>
+      </c>
+      <c r="F88" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="G88">
+        <v>25787</v>
+      </c>
+      <c r="H88">
+        <v>5157</v>
+      </c>
+      <c r="I88">
+        <v>2578</v>
+      </c>
+      <c r="J88">
+        <v>4235</v>
+      </c>
+      <c r="K88">
+        <v>37757</v>
+      </c>
+      <c r="L88">
+        <v>3094</v>
+      </c>
+      <c r="M88">
+        <v>3775</v>
+      </c>
+      <c r="N88">
+        <v>30888</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>71</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Pooja</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Mishra</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E89" t="str">
+        <v>HR</v>
+      </c>
+      <c r="F89" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="G89">
+        <v>25713</v>
+      </c>
+      <c r="H89">
+        <v>5142</v>
+      </c>
+      <c r="I89">
+        <v>2571</v>
+      </c>
+      <c r="J89">
+        <v>7926</v>
+      </c>
+      <c r="K89">
+        <v>41352</v>
+      </c>
+      <c r="L89">
+        <v>3085</v>
+      </c>
+      <c r="M89">
+        <v>4135</v>
+      </c>
+      <c r="N89">
+        <v>34132</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>40</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Yash</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Sharma</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E90" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="F90" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G90">
+        <v>24936</v>
+      </c>
+      <c r="H90">
+        <v>4987</v>
+      </c>
+      <c r="I90">
+        <v>2493</v>
+      </c>
+      <c r="J90">
+        <v>8770</v>
+      </c>
+      <c r="K90">
+        <v>41186</v>
+      </c>
+      <c r="L90">
+        <v>2992</v>
+      </c>
+      <c r="M90">
+        <v>4118</v>
+      </c>
+      <c r="N90">
+        <v>34076</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>51</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Komal</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Kumar</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E91" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="F91" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="G91">
+        <v>24916</v>
+      </c>
+      <c r="H91">
+        <v>4983</v>
+      </c>
+      <c r="I91">
+        <v>2491</v>
+      </c>
+      <c r="J91">
+        <v>7396</v>
+      </c>
+      <c r="K91">
+        <v>39786</v>
+      </c>
+      <c r="L91">
+        <v>2989</v>
+      </c>
+      <c r="M91">
+        <v>3978</v>
+      </c>
+      <c r="N91">
+        <v>32819</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>13</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Sneha</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Singh</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E92" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="F92" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="G92">
+        <v>24516</v>
+      </c>
+      <c r="H92">
+        <v>4903</v>
+      </c>
+      <c r="I92">
+        <v>2451</v>
+      </c>
+      <c r="J92">
+        <v>3791</v>
+      </c>
+      <c r="K92">
+        <v>35661</v>
+      </c>
+      <c r="L92">
+        <v>2941</v>
+      </c>
+      <c r="M92">
+        <v>3566</v>
+      </c>
+      <c r="N92">
+        <v>29154</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>62</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Vivek</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Verma</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E93" t="str">
+        <v>HR</v>
+      </c>
+      <c r="F93" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="G93">
+        <v>24418</v>
+      </c>
+      <c r="H93">
+        <v>4883</v>
+      </c>
+      <c r="I93">
+        <v>2441</v>
+      </c>
+      <c r="J93">
+        <v>3159</v>
+      </c>
+      <c r="K93">
+        <v>34901</v>
+      </c>
+      <c r="L93">
+        <v>2930</v>
+      </c>
+      <c r="M93">
+        <v>3490</v>
+      </c>
+      <c r="N93">
+        <v>28481</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>68</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Isha</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Naidu</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E94" t="str">
+        <v>IT</v>
+      </c>
+      <c r="F94" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G94">
+        <v>24203</v>
+      </c>
+      <c r="H94">
+        <v>4840</v>
+      </c>
+      <c r="I94">
+        <v>2420</v>
+      </c>
+      <c r="J94">
+        <v>9173</v>
+      </c>
+      <c r="K94">
+        <v>40636</v>
+      </c>
+      <c r="L94">
+        <v>2904</v>
+      </c>
+      <c r="M94">
+        <v>4063</v>
+      </c>
+      <c r="N94">
+        <v>33669</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>89</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Nisha</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Desai</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E95" t="str">
+        <v>IT</v>
+      </c>
+      <c r="F95" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G95">
+        <v>23348</v>
+      </c>
+      <c r="H95">
+        <v>4669</v>
+      </c>
+      <c r="I95">
+        <v>2334</v>
+      </c>
+      <c r="J95">
+        <v>9674</v>
+      </c>
+      <c r="K95">
+        <v>40025</v>
+      </c>
+      <c r="L95">
+        <v>2801</v>
+      </c>
+      <c r="M95">
+        <v>4002</v>
+      </c>
+      <c r="N95">
+        <v>33222</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>24</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Rahul</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Pillai</v>
+      </c>
+      <c r="D96" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E96" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="F96" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="G96">
+        <v>21817</v>
+      </c>
+      <c r="H96">
+        <v>4363</v>
+      </c>
+      <c r="I96">
+        <v>2181</v>
+      </c>
+      <c r="J96">
+        <v>3914</v>
+      </c>
+      <c r="K96">
+        <v>32275</v>
+      </c>
+      <c r="L96">
+        <v>2618</v>
+      </c>
+      <c r="M96">
+        <v>3227</v>
+      </c>
+      <c r="N96">
+        <v>26430</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>64</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Swati</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Reddy</v>
+      </c>
+      <c r="D97" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E97" t="str">
+        <v>HR</v>
+      </c>
+      <c r="F97" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="G97">
+        <v>21661</v>
+      </c>
+      <c r="H97">
+        <v>4332</v>
+      </c>
+      <c r="I97">
+        <v>2166</v>
+      </c>
+      <c r="J97">
+        <v>2432</v>
+      </c>
+      <c r="K97">
+        <v>30591</v>
+      </c>
+      <c r="L97">
+        <v>2599</v>
+      </c>
+      <c r="M97">
+        <v>3059</v>
+      </c>
+      <c r="N97">
+        <v>24933</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>85</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Gaurav</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Nair</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E98" t="str">
+        <v>IT</v>
+      </c>
+      <c r="F98" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="G98">
+        <v>20701</v>
+      </c>
+      <c r="H98">
+        <v>4140</v>
+      </c>
+      <c r="I98">
+        <v>2070</v>
+      </c>
+      <c r="J98">
+        <v>2014</v>
+      </c>
+      <c r="K98">
+        <v>28925</v>
+      </c>
+      <c r="L98">
+        <v>2484</v>
+      </c>
+      <c r="M98">
+        <v>2892</v>
+      </c>
+      <c r="N98">
+        <v>23549</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>38</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Tanuja</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Desai</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E99" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F99" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="G99">
+        <v>20380</v>
+      </c>
+      <c r="H99">
+        <v>4076</v>
+      </c>
+      <c r="I99">
+        <v>2038</v>
+      </c>
+      <c r="J99">
+        <v>8075</v>
+      </c>
+      <c r="K99">
+        <v>34569</v>
+      </c>
+      <c r="L99">
+        <v>2445</v>
+      </c>
+      <c r="M99">
+        <v>3456</v>
+      </c>
+      <c r="N99">
+        <v>28668</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>98</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Suresh</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Patel</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E100" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="F100" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="G100">
+        <v>20313</v>
+      </c>
+      <c r="H100">
+        <v>4062</v>
+      </c>
+      <c r="I100">
+        <v>2031</v>
+      </c>
+      <c r="J100">
+        <v>6573</v>
+      </c>
+      <c r="K100">
+        <v>32979</v>
+      </c>
+      <c r="L100">
+        <v>2437</v>
+      </c>
+      <c r="M100">
+        <v>3297</v>
+      </c>
+      <c r="N100">
+        <v>27245</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>55</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Aarti</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Nair</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E101" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="F101" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="G101">
+        <v>20000</v>
+      </c>
+      <c r="H101">
+        <v>4000</v>
+      </c>
+      <c r="I101">
+        <v>2000</v>
+      </c>
+      <c r="J101">
+        <v>3589</v>
+      </c>
+      <c r="K101">
+        <v>29589</v>
+      </c>
+      <c r="L101">
+        <v>2400</v>
+      </c>
+      <c r="M101">
+        <v>2958</v>
+      </c>
+      <c r="N101">
+        <v>24231</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EF385FA-25BF-4CBD-9896-74ED0EC16CC8}">
+  <dimension ref="A1:N54"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" cm="1">
+        <f t="array" ref="A4:N54">_xlfn._xlws.FILTER('Employee Data'!A2:N101,'Employee Data'!D2:D101="Male","Not Found")</f>
+        <v>1</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Deepak</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Singh</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="G4">
+        <v>58591</v>
+      </c>
+      <c r="H4">
+        <v>11718</v>
+      </c>
+      <c r="I4">
+        <v>5859</v>
+      </c>
+      <c r="J4">
+        <v>3532</v>
+      </c>
+      <c r="K4">
+        <v>79700</v>
+      </c>
+      <c r="L4">
+        <v>7030</v>
+      </c>
+      <c r="M4">
+        <v>7970</v>
+      </c>
+      <c r="N4">
+        <v>64700</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Varun</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Joshi</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E5" t="str">
+        <v>HR</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="G5">
+        <v>48337</v>
+      </c>
+      <c r="H5">
+        <v>9667</v>
+      </c>
+      <c r="I5">
+        <v>4833</v>
+      </c>
+      <c r="J5">
+        <v>4065</v>
+      </c>
+      <c r="K5">
+        <v>66902</v>
+      </c>
+      <c r="L5">
+        <v>5800</v>
+      </c>
+      <c r="M5">
+        <v>6690</v>
+      </c>
+      <c r="N5">
+        <v>54412</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Vivek</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Kumar</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G6">
+        <v>68374</v>
+      </c>
+      <c r="H6">
+        <v>13674</v>
+      </c>
+      <c r="I6">
+        <v>6837</v>
+      </c>
+      <c r="J6">
+        <v>7208</v>
+      </c>
+      <c r="K6">
+        <v>96093</v>
+      </c>
+      <c r="L6">
+        <v>8204</v>
+      </c>
+      <c r="M6">
+        <v>9609</v>
+      </c>
+      <c r="N6">
+        <v>78280</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Arjun</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Kulkarni</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G7">
+        <v>29057</v>
+      </c>
+      <c r="H7">
+        <v>5811</v>
+      </c>
+      <c r="I7">
+        <v>2905</v>
+      </c>
+      <c r="J7">
+        <v>4753</v>
+      </c>
+      <c r="K7">
+        <v>42526</v>
+      </c>
+      <c r="L7">
+        <v>3486</v>
+      </c>
+      <c r="M7">
+        <v>4252</v>
+      </c>
+      <c r="N7">
+        <v>34788</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Arjun</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Sharma</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G8">
+        <v>29593</v>
+      </c>
+      <c r="H8">
+        <v>5918</v>
+      </c>
+      <c r="I8">
+        <v>2959</v>
+      </c>
+      <c r="J8">
+        <v>9188</v>
+      </c>
+      <c r="K8">
+        <v>47658</v>
+      </c>
+      <c r="L8">
+        <v>3551</v>
+      </c>
+      <c r="M8">
+        <v>4765</v>
+      </c>
+      <c r="N8">
+        <v>39342</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Suresh</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Verma</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G9">
+        <v>75829</v>
+      </c>
+      <c r="H9">
+        <v>15165</v>
+      </c>
+      <c r="I9">
+        <v>7582</v>
+      </c>
+      <c r="J9">
+        <v>9631</v>
+      </c>
+      <c r="K9">
+        <v>108207</v>
+      </c>
+      <c r="L9">
+        <v>9099</v>
+      </c>
+      <c r="M9">
+        <v>10820</v>
+      </c>
+      <c r="N9">
+        <v>88288</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>10</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Rahul</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Mishra</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="G10">
+        <v>67435</v>
+      </c>
+      <c r="H10">
+        <v>13487</v>
+      </c>
+      <c r="I10">
+        <v>6743</v>
+      </c>
+      <c r="J10">
+        <v>9563</v>
+      </c>
+      <c r="K10">
+        <v>97228</v>
+      </c>
+      <c r="L10">
+        <v>8092</v>
+      </c>
+      <c r="M10">
+        <v>9722</v>
+      </c>
+      <c r="N10">
+        <v>79414</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>12</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Karan</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Mehta</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G11">
+        <v>48524</v>
+      </c>
+      <c r="H11">
+        <v>9704</v>
+      </c>
+      <c r="I11">
+        <v>4852</v>
+      </c>
+      <c r="J11">
+        <v>2310</v>
+      </c>
+      <c r="K11">
+        <v>65390</v>
+      </c>
+      <c r="L11">
+        <v>5822</v>
+      </c>
+      <c r="M11">
+        <v>6539</v>
+      </c>
+      <c r="N11">
+        <v>53029</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>14</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Ramesh</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Kulkarni</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G12">
+        <v>74084</v>
+      </c>
+      <c r="H12">
+        <v>14816</v>
+      </c>
+      <c r="I12">
+        <v>7408</v>
+      </c>
+      <c r="J12">
+        <v>3612</v>
+      </c>
+      <c r="K12">
+        <v>99920</v>
+      </c>
+      <c r="L12">
+        <v>8890</v>
+      </c>
+      <c r="M12">
+        <v>9992</v>
+      </c>
+      <c r="N12">
+        <v>81038</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>16</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Ramesh</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Pillai</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G13">
+        <v>59401</v>
+      </c>
+      <c r="H13">
+        <v>11880</v>
+      </c>
+      <c r="I13">
+        <v>5940</v>
+      </c>
+      <c r="J13">
+        <v>8652</v>
+      </c>
+      <c r="K13">
+        <v>85873</v>
+      </c>
+      <c r="L13">
+        <v>7128</v>
+      </c>
+      <c r="M13">
+        <v>8587</v>
+      </c>
+      <c r="N13">
+        <v>70158</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>20</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Manish</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Gupta</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G14">
+        <v>44462</v>
+      </c>
+      <c r="H14">
+        <v>8892</v>
+      </c>
+      <c r="I14">
+        <v>4446</v>
+      </c>
+      <c r="J14">
+        <v>3086</v>
+      </c>
+      <c r="K14">
+        <v>60886</v>
+      </c>
+      <c r="L14">
+        <v>5335</v>
+      </c>
+      <c r="M14">
+        <v>6088</v>
+      </c>
+      <c r="N14">
+        <v>49463</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>21</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Amit</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Pillai</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="G15">
+        <v>79664</v>
+      </c>
+      <c r="H15">
+        <v>15932</v>
+      </c>
+      <c r="I15">
+        <v>7966</v>
+      </c>
+      <c r="J15">
+        <v>8826</v>
+      </c>
+      <c r="K15">
+        <v>112388</v>
+      </c>
+      <c r="L15">
+        <v>9559</v>
+      </c>
+      <c r="M15">
+        <v>11238</v>
+      </c>
+      <c r="N15">
+        <v>91591</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>24</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Rahul</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Pillai</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="G16">
+        <v>21817</v>
+      </c>
+      <c r="H16">
+        <v>4363</v>
+      </c>
+      <c r="I16">
+        <v>2181</v>
+      </c>
+      <c r="J16">
+        <v>3914</v>
+      </c>
+      <c r="K16">
+        <v>32275</v>
+      </c>
+      <c r="L16">
+        <v>2618</v>
+      </c>
+      <c r="M16">
+        <v>3227</v>
+      </c>
+      <c r="N16">
+        <v>26430</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>25</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Sanjay</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Patel</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E17" t="str">
+        <v>IT</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G17">
+        <v>58962</v>
+      </c>
+      <c r="H17">
+        <v>11792</v>
+      </c>
+      <c r="I17">
+        <v>5896</v>
+      </c>
+      <c r="J17">
+        <v>6829</v>
+      </c>
+      <c r="K17">
+        <v>83479</v>
+      </c>
+      <c r="L17">
+        <v>7075</v>
+      </c>
+      <c r="M17">
+        <v>8347</v>
+      </c>
+      <c r="N17">
+        <v>68057</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>27</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Ramesh</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Gupta</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E18" t="str">
+        <v>IT</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="G18">
+        <v>78665</v>
+      </c>
+      <c r="H18">
+        <v>15733</v>
+      </c>
+      <c r="I18">
+        <v>7866</v>
+      </c>
+      <c r="J18">
+        <v>3924</v>
+      </c>
+      <c r="K18">
+        <v>106188</v>
+      </c>
+      <c r="L18">
+        <v>9439</v>
+      </c>
+      <c r="M18">
+        <v>10618</v>
+      </c>
+      <c r="N18">
+        <v>86131</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>28</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Ramesh</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Yadav</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E19" t="str">
+        <v>HR</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="G19">
+        <v>47308</v>
+      </c>
+      <c r="H19">
+        <v>9461</v>
+      </c>
+      <c r="I19">
+        <v>4730</v>
+      </c>
+      <c r="J19">
+        <v>8299</v>
+      </c>
+      <c r="K19">
+        <v>69798</v>
+      </c>
+      <c r="L19">
+        <v>5676</v>
+      </c>
+      <c r="M19">
+        <v>6979</v>
+      </c>
+      <c r="N19">
+        <v>57143</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>29</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Varun</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Iyer</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="G20">
+        <v>63476</v>
+      </c>
+      <c r="H20">
+        <v>12695</v>
+      </c>
+      <c r="I20">
+        <v>6347</v>
+      </c>
+      <c r="J20">
+        <v>4326</v>
+      </c>
+      <c r="K20">
+        <v>86844</v>
+      </c>
+      <c r="L20">
+        <v>7617</v>
+      </c>
+      <c r="M20">
+        <v>8684</v>
+      </c>
+      <c r="N20">
+        <v>70543</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>30</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Rohit</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Singh</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G21">
+        <v>70224</v>
+      </c>
+      <c r="H21">
+        <v>14044</v>
+      </c>
+      <c r="I21">
+        <v>7022</v>
+      </c>
+      <c r="J21">
+        <v>2902</v>
+      </c>
+      <c r="K21">
+        <v>94192</v>
+      </c>
+      <c r="L21">
+        <v>8426</v>
+      </c>
+      <c r="M21">
+        <v>9419</v>
+      </c>
+      <c r="N21">
+        <v>76347</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>31</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Ramesh</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Patel</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="G22">
+        <v>57847</v>
+      </c>
+      <c r="H22">
+        <v>11569</v>
+      </c>
+      <c r="I22">
+        <v>5784</v>
+      </c>
+      <c r="J22">
+        <v>5757</v>
+      </c>
+      <c r="K22">
+        <v>80957</v>
+      </c>
+      <c r="L22">
+        <v>6941</v>
+      </c>
+      <c r="M22">
+        <v>8095</v>
+      </c>
+      <c r="N22">
+        <v>65921</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>33</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Deepak</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Iyer</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="G23">
+        <v>34427</v>
+      </c>
+      <c r="H23">
+        <v>6885</v>
+      </c>
+      <c r="I23">
+        <v>3442</v>
+      </c>
+      <c r="J23">
+        <v>5668</v>
+      </c>
+      <c r="K23">
+        <v>50422</v>
+      </c>
+      <c r="L23">
+        <v>4131</v>
+      </c>
+      <c r="M23">
+        <v>5042</v>
+      </c>
+      <c r="N23">
+        <v>41249</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>36</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Amit</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Bose</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="G24">
+        <v>47876</v>
+      </c>
+      <c r="H24">
+        <v>9575</v>
+      </c>
+      <c r="I24">
+        <v>4787</v>
+      </c>
+      <c r="J24">
+        <v>6335</v>
+      </c>
+      <c r="K24">
+        <v>68573</v>
+      </c>
+      <c r="L24">
+        <v>5745</v>
+      </c>
+      <c r="M24">
+        <v>6857</v>
+      </c>
+      <c r="N24">
+        <v>55971</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>37</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Suresh</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Nair</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="G25">
+        <v>45653</v>
+      </c>
+      <c r="H25">
+        <v>9130</v>
+      </c>
+      <c r="I25">
+        <v>4565</v>
+      </c>
+      <c r="J25">
+        <v>7327</v>
+      </c>
+      <c r="K25">
+        <v>66675</v>
+      </c>
+      <c r="L25">
+        <v>5478</v>
+      </c>
+      <c r="M25">
+        <v>6667</v>
+      </c>
+      <c r="N25">
+        <v>54530</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>40</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Yash</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Sharma</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G26">
+        <v>24936</v>
+      </c>
+      <c r="H26">
+        <v>4987</v>
+      </c>
+      <c r="I26">
+        <v>2493</v>
+      </c>
+      <c r="J26">
+        <v>8770</v>
+      </c>
+      <c r="K26">
+        <v>41186</v>
+      </c>
+      <c r="L26">
+        <v>2992</v>
+      </c>
+      <c r="M26">
+        <v>4118</v>
+      </c>
+      <c r="N26">
+        <v>34076</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>41</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Arjun</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Nair</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E27" t="str">
+        <v>IT</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="G27">
+        <v>72163</v>
+      </c>
+      <c r="H27">
+        <v>14432</v>
+      </c>
+      <c r="I27">
+        <v>7216</v>
+      </c>
+      <c r="J27">
+        <v>6978</v>
+      </c>
+      <c r="K27">
+        <v>100789</v>
+      </c>
+      <c r="L27">
+        <v>8659</v>
+      </c>
+      <c r="M27">
+        <v>10078</v>
+      </c>
+      <c r="N27">
+        <v>82052</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>42</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Harish</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Reddy</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E28" t="str">
+        <v>IT</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G28">
+        <v>29984</v>
+      </c>
+      <c r="H28">
+        <v>5996</v>
+      </c>
+      <c r="I28">
+        <v>2998</v>
+      </c>
+      <c r="J28">
+        <v>2533</v>
+      </c>
+      <c r="K28">
+        <v>41511</v>
+      </c>
+      <c r="L28">
+        <v>3598</v>
+      </c>
+      <c r="M28">
+        <v>4151</v>
+      </c>
+      <c r="N28">
+        <v>33762</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>45</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Gaurav</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Verma</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E29" t="str">
+        <v>HR</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G29">
+        <v>53871</v>
+      </c>
+      <c r="H29">
+        <v>10774</v>
+      </c>
+      <c r="I29">
+        <v>5387</v>
+      </c>
+      <c r="J29">
+        <v>9976</v>
+      </c>
+      <c r="K29">
+        <v>80008</v>
+      </c>
+      <c r="L29">
+        <v>6464</v>
+      </c>
+      <c r="M29">
+        <v>8000</v>
+      </c>
+      <c r="N29">
+        <v>65544</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>47</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Harish</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Verma</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="G30">
+        <v>32824</v>
+      </c>
+      <c r="H30">
+        <v>6564</v>
+      </c>
+      <c r="I30">
+        <v>3282</v>
+      </c>
+      <c r="J30">
+        <v>9464</v>
+      </c>
+      <c r="K30">
+        <v>52134</v>
+      </c>
+      <c r="L30">
+        <v>3938</v>
+      </c>
+      <c r="M30">
+        <v>5213</v>
+      </c>
+      <c r="N30">
+        <v>42983</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>49</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Ramesh</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Singh</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G31">
+        <v>71786</v>
+      </c>
+      <c r="H31">
+        <v>14357</v>
+      </c>
+      <c r="I31">
+        <v>7178</v>
+      </c>
+      <c r="J31">
+        <v>3357</v>
+      </c>
+      <c r="K31">
+        <v>96678</v>
+      </c>
+      <c r="L31">
+        <v>8614</v>
+      </c>
+      <c r="M31">
+        <v>9667</v>
+      </c>
+      <c r="N31">
+        <v>78397</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>52</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Gaurav</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Desai</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G32">
+        <v>79232</v>
+      </c>
+      <c r="H32">
+        <v>15846</v>
+      </c>
+      <c r="I32">
+        <v>7923</v>
+      </c>
+      <c r="J32">
+        <v>7211</v>
+      </c>
+      <c r="K32">
+        <v>110212</v>
+      </c>
+      <c r="L32">
+        <v>9507</v>
+      </c>
+      <c r="M32">
+        <v>11021</v>
+      </c>
+      <c r="N32">
+        <v>89684</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>54</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Nikhil</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Verma</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E33" t="str">
+        <v>HR</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G33">
+        <v>40881</v>
+      </c>
+      <c r="H33">
+        <v>8176</v>
+      </c>
+      <c r="I33">
+        <v>4088</v>
+      </c>
+      <c r="J33">
+        <v>3607</v>
+      </c>
+      <c r="K33">
+        <v>56752</v>
+      </c>
+      <c r="L33">
+        <v>4905</v>
+      </c>
+      <c r="M33">
+        <v>5675</v>
+      </c>
+      <c r="N33">
+        <v>46172</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>60</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Nikhil</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Mishra</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="G34">
+        <v>33947</v>
+      </c>
+      <c r="H34">
+        <v>6789</v>
+      </c>
+      <c r="I34">
+        <v>3394</v>
+      </c>
+      <c r="J34">
+        <v>3524</v>
+      </c>
+      <c r="K34">
+        <v>47654</v>
+      </c>
+      <c r="L34">
+        <v>4073</v>
+      </c>
+      <c r="M34">
+        <v>4765</v>
+      </c>
+      <c r="N34">
+        <v>38816</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>62</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Vivek</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Verma</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E35" t="str">
+        <v>HR</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="G35">
+        <v>24418</v>
+      </c>
+      <c r="H35">
+        <v>4883</v>
+      </c>
+      <c r="I35">
+        <v>2441</v>
+      </c>
+      <c r="J35">
+        <v>3159</v>
+      </c>
+      <c r="K35">
+        <v>34901</v>
+      </c>
+      <c r="L35">
+        <v>2930</v>
+      </c>
+      <c r="M35">
+        <v>3490</v>
+      </c>
+      <c r="N35">
+        <v>28481</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>66</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Vikas</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Joshi</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="G36">
+        <v>36378</v>
+      </c>
+      <c r="H36">
+        <v>7275</v>
+      </c>
+      <c r="I36">
+        <v>3637</v>
+      </c>
+      <c r="J36">
+        <v>5600</v>
+      </c>
+      <c r="K36">
+        <v>52890</v>
+      </c>
+      <c r="L36">
+        <v>4365</v>
+      </c>
+      <c r="M36">
+        <v>5289</v>
+      </c>
+      <c r="N36">
+        <v>43236</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>67</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Harish</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Das</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E37" t="str">
+        <v>IT</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G37">
+        <v>26916</v>
+      </c>
+      <c r="H37">
+        <v>5383</v>
+      </c>
+      <c r="I37">
+        <v>2691</v>
+      </c>
+      <c r="J37">
+        <v>5457</v>
+      </c>
+      <c r="K37">
+        <v>40447</v>
+      </c>
+      <c r="L37">
+        <v>3229</v>
+      </c>
+      <c r="M37">
+        <v>4044</v>
+      </c>
+      <c r="N37">
+        <v>33174</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>69</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Sanjay</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Mishra</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="G38">
+        <v>57318</v>
+      </c>
+      <c r="H38">
+        <v>11463</v>
+      </c>
+      <c r="I38">
+        <v>5731</v>
+      </c>
+      <c r="J38">
+        <v>5077</v>
+      </c>
+      <c r="K38">
+        <v>79589</v>
+      </c>
+      <c r="L38">
+        <v>6878</v>
+      </c>
+      <c r="M38">
+        <v>7958</v>
+      </c>
+      <c r="N38">
+        <v>64753</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>73</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Deepak</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Gupta</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="G39">
+        <v>70564</v>
+      </c>
+      <c r="H39">
+        <v>14112</v>
+      </c>
+      <c r="I39">
+        <v>7056</v>
+      </c>
+      <c r="J39">
+        <v>9182</v>
+      </c>
+      <c r="K39">
+        <v>100914</v>
+      </c>
+      <c r="L39">
+        <v>8467</v>
+      </c>
+      <c r="M39">
+        <v>10091</v>
+      </c>
+      <c r="N39">
+        <v>82356</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>74</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Rahul</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Verma</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="G40">
+        <v>79526</v>
+      </c>
+      <c r="H40">
+        <v>15905</v>
+      </c>
+      <c r="I40">
+        <v>7952</v>
+      </c>
+      <c r="J40">
+        <v>6990</v>
+      </c>
+      <c r="K40">
+        <v>110373</v>
+      </c>
+      <c r="L40">
+        <v>9543</v>
+      </c>
+      <c r="M40">
+        <v>11037</v>
+      </c>
+      <c r="N40">
+        <v>89793</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>76</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Karan</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Patel</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E41" t="str">
+        <v>HR</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="G41">
+        <v>25887</v>
+      </c>
+      <c r="H41">
+        <v>5177</v>
+      </c>
+      <c r="I41">
+        <v>2588</v>
+      </c>
+      <c r="J41">
+        <v>9023</v>
+      </c>
+      <c r="K41">
+        <v>42675</v>
+      </c>
+      <c r="L41">
+        <v>3106</v>
+      </c>
+      <c r="M41">
+        <v>4267</v>
+      </c>
+      <c r="N41">
+        <v>35302</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>77</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Rahul</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Iyer</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="G42">
+        <v>34264</v>
+      </c>
+      <c r="H42">
+        <v>6852</v>
+      </c>
+      <c r="I42">
+        <v>3426</v>
+      </c>
+      <c r="J42">
+        <v>9643</v>
+      </c>
+      <c r="K42">
+        <v>54185</v>
+      </c>
+      <c r="L42">
+        <v>4111</v>
+      </c>
+      <c r="M42">
+        <v>5418</v>
+      </c>
+      <c r="N42">
+        <v>44656</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>78</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Ramesh</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Verma</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="G43">
+        <v>52061</v>
+      </c>
+      <c r="H43">
+        <v>10412</v>
+      </c>
+      <c r="I43">
+        <v>5206</v>
+      </c>
+      <c r="J43">
+        <v>6800</v>
+      </c>
+      <c r="K43">
+        <v>74479</v>
+      </c>
+      <c r="L43">
+        <v>6247</v>
+      </c>
+      <c r="M43">
+        <v>7447</v>
+      </c>
+      <c r="N43">
+        <v>60785</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>79</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Vikas</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Nair</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E44" t="str">
+        <v>IT</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="G44">
+        <v>55880</v>
+      </c>
+      <c r="H44">
+        <v>11176</v>
+      </c>
+      <c r="I44">
+        <v>5588</v>
+      </c>
+      <c r="J44">
+        <v>4176</v>
+      </c>
+      <c r="K44">
+        <v>76820</v>
+      </c>
+      <c r="L44">
+        <v>6705</v>
+      </c>
+      <c r="M44">
+        <v>7682</v>
+      </c>
+      <c r="N44">
+        <v>62433</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>82</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Akash</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Joshi</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="G45">
+        <v>58807</v>
+      </c>
+      <c r="H45">
+        <v>11761</v>
+      </c>
+      <c r="I45">
+        <v>5880</v>
+      </c>
+      <c r="J45">
+        <v>6518</v>
+      </c>
+      <c r="K45">
+        <v>82966</v>
+      </c>
+      <c r="L45">
+        <v>7056</v>
+      </c>
+      <c r="M45">
+        <v>8296</v>
+      </c>
+      <c r="N45">
+        <v>67614</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>83</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Manish</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Desai</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="G46">
+        <v>65463</v>
+      </c>
+      <c r="H46">
+        <v>13092</v>
+      </c>
+      <c r="I46">
+        <v>6546</v>
+      </c>
+      <c r="J46">
+        <v>6107</v>
+      </c>
+      <c r="K46">
+        <v>91208</v>
+      </c>
+      <c r="L46">
+        <v>7855</v>
+      </c>
+      <c r="M46">
+        <v>9120</v>
+      </c>
+      <c r="N46">
+        <v>74233</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>84</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Anil</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Kulkarni</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G47">
+        <v>44075</v>
+      </c>
+      <c r="H47">
+        <v>8815</v>
+      </c>
+      <c r="I47">
+        <v>4407</v>
+      </c>
+      <c r="J47">
+        <v>9661</v>
+      </c>
+      <c r="K47">
+        <v>66958</v>
+      </c>
+      <c r="L47">
+        <v>5289</v>
+      </c>
+      <c r="M47">
+        <v>6695</v>
+      </c>
+      <c r="N47">
+        <v>54974</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>85</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Gaurav</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Nair</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E48" t="str">
+        <v>IT</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="G48">
+        <v>20701</v>
+      </c>
+      <c r="H48">
+        <v>4140</v>
+      </c>
+      <c r="I48">
+        <v>2070</v>
+      </c>
+      <c r="J48">
+        <v>2014</v>
+      </c>
+      <c r="K48">
+        <v>28925</v>
+      </c>
+      <c r="L48">
+        <v>2484</v>
+      </c>
+      <c r="M48">
+        <v>2892</v>
+      </c>
+      <c r="N48">
+        <v>23549</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>87</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Yash</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Reddy</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G49">
+        <v>65347</v>
+      </c>
+      <c r="H49">
+        <v>13069</v>
+      </c>
+      <c r="I49">
+        <v>6534</v>
+      </c>
+      <c r="J49">
+        <v>7333</v>
+      </c>
+      <c r="K49">
+        <v>92283</v>
+      </c>
+      <c r="L49">
+        <v>7841</v>
+      </c>
+      <c r="M49">
+        <v>9228</v>
+      </c>
+      <c r="N49">
+        <v>75214</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>90</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Nikhil</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Naidu</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="G50">
+        <v>47602</v>
+      </c>
+      <c r="H50">
+        <v>9520</v>
+      </c>
+      <c r="I50">
+        <v>4760</v>
+      </c>
+      <c r="J50">
+        <v>3250</v>
+      </c>
+      <c r="K50">
+        <v>65132</v>
+      </c>
+      <c r="L50">
+        <v>5712</v>
+      </c>
+      <c r="M50">
+        <v>6513</v>
+      </c>
+      <c r="N50">
+        <v>52907</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>93</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Vivek</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Naidu</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G51">
+        <v>75458</v>
+      </c>
+      <c r="H51">
+        <v>15091</v>
+      </c>
+      <c r="I51">
+        <v>7545</v>
+      </c>
+      <c r="J51">
+        <v>2729</v>
+      </c>
+      <c r="K51">
+        <v>100823</v>
+      </c>
+      <c r="L51">
+        <v>9054</v>
+      </c>
+      <c r="M51">
+        <v>10082</v>
+      </c>
+      <c r="N51">
+        <v>81687</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>94</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Deepak</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Yadav</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E52" t="str">
+        <v>HR</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="G52">
+        <v>64799</v>
+      </c>
+      <c r="H52">
+        <v>12959</v>
+      </c>
+      <c r="I52">
+        <v>6479</v>
+      </c>
+      <c r="J52">
+        <v>9314</v>
+      </c>
+      <c r="K52">
+        <v>93551</v>
+      </c>
+      <c r="L52">
+        <v>7775</v>
+      </c>
+      <c r="M52">
+        <v>9355</v>
+      </c>
+      <c r="N52">
+        <v>76421</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>98</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Suresh</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Patel</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="F53" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="G53">
+        <v>20313</v>
+      </c>
+      <c r="H53">
+        <v>4062</v>
+      </c>
+      <c r="I53">
+        <v>2031</v>
+      </c>
+      <c r="J53">
+        <v>6573</v>
+      </c>
+      <c r="K53">
+        <v>32979</v>
+      </c>
+      <c r="L53">
+        <v>2437</v>
+      </c>
+      <c r="M53">
+        <v>3297</v>
+      </c>
+      <c r="N53">
+        <v>27245</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>99</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Prakash</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Iyer</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="F54" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="G54">
+        <v>41685</v>
+      </c>
+      <c r="H54">
+        <v>8337</v>
+      </c>
+      <c r="I54">
+        <v>4168</v>
+      </c>
+      <c r="J54">
+        <v>9202</v>
+      </c>
+      <c r="K54">
+        <v>63392</v>
+      </c>
+      <c r="L54">
+        <v>5002</v>
+      </c>
+      <c r="M54">
+        <v>6339</v>
+      </c>
+      <c r="N54">
+        <v>52051</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7AB7172-1A1D-484E-94A0-D10BDE8730A5}">
+  <dimension ref="A1:AG52"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="G2" t="s">
+        <v>93</v>
+      </c>
+      <c r="T2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M3" t="s">
+        <v>9</v>
+      </c>
+      <c r="N3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T3" t="s">
+        <v>0</v>
+      </c>
+      <c r="U3" t="s">
+        <v>1</v>
+      </c>
+      <c r="V3" t="s">
+        <v>2</v>
+      </c>
+      <c r="W3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" cm="1">
+        <f t="array" ref="D4:Q52">_xlfn._xlws.FILTER('Employee Data'!A2:N101,'Employee Data'!D2:D101=B3,"Not Found")</f>
+        <v>2</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Swati</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Mishra</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="J4">
+        <v>70205</v>
+      </c>
+      <c r="K4">
+        <v>14041</v>
+      </c>
+      <c r="L4">
+        <v>7020</v>
+      </c>
+      <c r="M4">
+        <v>5973</v>
+      </c>
+      <c r="N4">
+        <v>97239</v>
+      </c>
+      <c r="O4">
+        <v>8424</v>
+      </c>
+      <c r="P4">
+        <v>9723</v>
+      </c>
+      <c r="Q4">
+        <v>79092</v>
+      </c>
+      <c r="T4" cm="1">
+        <f t="array" ref="T4:AG20">_xlfn._xlws.FILTER('Employee Data'!A2:N101,'Employee Data'!E2:E101=B4,"Not found")</f>
+        <v>5</v>
+      </c>
+      <c r="U4" t="str">
+        <v>Vivek</v>
+      </c>
+      <c r="V4" t="str">
+        <v>Kumar</v>
+      </c>
+      <c r="W4" t="str">
+        <v>Male</v>
+      </c>
+      <c r="X4" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="Y4" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="Z4">
+        <v>68374</v>
+      </c>
+      <c r="AA4">
+        <v>13674</v>
+      </c>
+      <c r="AB4">
+        <v>6837</v>
+      </c>
+      <c r="AC4">
+        <v>7208</v>
+      </c>
+      <c r="AD4">
+        <v>96093</v>
+      </c>
+      <c r="AE4">
+        <v>8204</v>
+      </c>
+      <c r="AF4">
+        <v>9609</v>
+      </c>
+      <c r="AG4">
+        <v>78280</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Sunita</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Naidu</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H5" t="str">
+        <v>HR</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="J5">
+        <v>62004</v>
+      </c>
+      <c r="K5">
+        <v>12400</v>
+      </c>
+      <c r="L5">
+        <v>6200</v>
+      </c>
+      <c r="M5">
+        <v>3965</v>
+      </c>
+      <c r="N5">
+        <v>84569</v>
+      </c>
+      <c r="O5">
+        <v>7440</v>
+      </c>
+      <c r="P5">
+        <v>8456</v>
+      </c>
+      <c r="Q5">
+        <v>68673</v>
+      </c>
+      <c r="T5">
+        <v>7</v>
+      </c>
+      <c r="U5" t="str">
+        <v>Arjun</v>
+      </c>
+      <c r="V5" t="str">
+        <v>Sharma</v>
+      </c>
+      <c r="W5" t="str">
+        <v>Male</v>
+      </c>
+      <c r="X5" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="Y5" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="Z5">
+        <v>29593</v>
+      </c>
+      <c r="AA5">
+        <v>5918</v>
+      </c>
+      <c r="AB5">
+        <v>2959</v>
+      </c>
+      <c r="AC5">
+        <v>9188</v>
+      </c>
+      <c r="AD5">
+        <v>47658</v>
+      </c>
+      <c r="AE5">
+        <v>3551</v>
+      </c>
+      <c r="AF5">
+        <v>4765</v>
+      </c>
+      <c r="AG5">
+        <v>39342</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Anjali</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Patel</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="J6">
+        <v>52037</v>
+      </c>
+      <c r="K6">
+        <v>10407</v>
+      </c>
+      <c r="L6">
+        <v>5203</v>
+      </c>
+      <c r="M6">
+        <v>4853</v>
+      </c>
+      <c r="N6">
+        <v>72500</v>
+      </c>
+      <c r="O6">
+        <v>6244</v>
+      </c>
+      <c r="P6">
+        <v>7250</v>
+      </c>
+      <c r="Q6">
+        <v>59006</v>
+      </c>
+      <c r="T6">
+        <v>8</v>
+      </c>
+      <c r="U6" t="str">
+        <v>Suresh</v>
+      </c>
+      <c r="V6" t="str">
+        <v>Verma</v>
+      </c>
+      <c r="W6" t="str">
+        <v>Male</v>
+      </c>
+      <c r="X6" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="Y6" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="Z6">
+        <v>75829</v>
+      </c>
+      <c r="AA6">
+        <v>15165</v>
+      </c>
+      <c r="AB6">
+        <v>7582</v>
+      </c>
+      <c r="AC6">
+        <v>9631</v>
+      </c>
+      <c r="AD6">
+        <v>108207</v>
+      </c>
+      <c r="AE6">
+        <v>9099</v>
+      </c>
+      <c r="AF6">
+        <v>10820</v>
+      </c>
+      <c r="AG6">
+        <v>88288</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="D7">
+        <v>11</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Rashmi</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Mishra</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="J7">
+        <v>52011</v>
+      </c>
+      <c r="K7">
+        <v>10402</v>
+      </c>
+      <c r="L7">
+        <v>5201</v>
+      </c>
+      <c r="M7">
+        <v>4542</v>
+      </c>
+      <c r="N7">
+        <v>72156</v>
+      </c>
+      <c r="O7">
+        <v>6241</v>
+      </c>
+      <c r="P7">
+        <v>7215</v>
+      </c>
+      <c r="Q7">
+        <v>58700</v>
+      </c>
+      <c r="T7">
+        <v>10</v>
+      </c>
+      <c r="U7" t="str">
+        <v>Rahul</v>
+      </c>
+      <c r="V7" t="str">
+        <v>Mishra</v>
+      </c>
+      <c r="W7" t="str">
+        <v>Male</v>
+      </c>
+      <c r="X7" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="Y7" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="Z7">
+        <v>67435</v>
+      </c>
+      <c r="AA7">
+        <v>13487</v>
+      </c>
+      <c r="AB7">
+        <v>6743</v>
+      </c>
+      <c r="AC7">
+        <v>9563</v>
+      </c>
+      <c r="AD7">
+        <v>97228</v>
+      </c>
+      <c r="AE7">
+        <v>8092</v>
+      </c>
+      <c r="AF7">
+        <v>9722</v>
+      </c>
+      <c r="AG7">
+        <v>79414</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="D8">
+        <v>13</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Sneha</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Singh</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="J8">
+        <v>24516</v>
+      </c>
+      <c r="K8">
+        <v>4903</v>
+      </c>
+      <c r="L8">
+        <v>2451</v>
+      </c>
+      <c r="M8">
+        <v>3791</v>
+      </c>
+      <c r="N8">
+        <v>35661</v>
+      </c>
+      <c r="O8">
+        <v>2941</v>
+      </c>
+      <c r="P8">
+        <v>3566</v>
+      </c>
+      <c r="Q8">
+        <v>29154</v>
+      </c>
+      <c r="T8">
+        <v>14</v>
+      </c>
+      <c r="U8" t="str">
+        <v>Ramesh</v>
+      </c>
+      <c r="V8" t="str">
+        <v>Kulkarni</v>
+      </c>
+      <c r="W8" t="str">
+        <v>Male</v>
+      </c>
+      <c r="X8" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="Y8" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="Z8">
+        <v>74084</v>
+      </c>
+      <c r="AA8">
+        <v>14816</v>
+      </c>
+      <c r="AB8">
+        <v>7408</v>
+      </c>
+      <c r="AC8">
+        <v>3612</v>
+      </c>
+      <c r="AD8">
+        <v>99920</v>
+      </c>
+      <c r="AE8">
+        <v>8890</v>
+      </c>
+      <c r="AF8">
+        <v>9992</v>
+      </c>
+      <c r="AG8">
+        <v>81038</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="D9">
+        <v>15</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Sneha</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Das</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="J9">
+        <v>54644</v>
+      </c>
+      <c r="K9">
+        <v>10928</v>
+      </c>
+      <c r="L9">
+        <v>5464</v>
+      </c>
+      <c r="M9">
+        <v>2644</v>
+      </c>
+      <c r="N9">
+        <v>73680</v>
+      </c>
+      <c r="O9">
+        <v>6557</v>
+      </c>
+      <c r="P9">
+        <v>7368</v>
+      </c>
+      <c r="Q9">
+        <v>59755</v>
+      </c>
+      <c r="T9">
+        <v>16</v>
+      </c>
+      <c r="U9" t="str">
+        <v>Ramesh</v>
+      </c>
+      <c r="V9" t="str">
+        <v>Pillai</v>
+      </c>
+      <c r="W9" t="str">
+        <v>Male</v>
+      </c>
+      <c r="X9" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="Y9" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="Z9">
+        <v>59401</v>
+      </c>
+      <c r="AA9">
+        <v>11880</v>
+      </c>
+      <c r="AB9">
+        <v>5940</v>
+      </c>
+      <c r="AC9">
+        <v>8652</v>
+      </c>
+      <c r="AD9">
+        <v>85873</v>
+      </c>
+      <c r="AE9">
+        <v>7128</v>
+      </c>
+      <c r="AF9">
+        <v>8587</v>
+      </c>
+      <c r="AG9">
+        <v>70158</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="D10">
+        <v>17</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Shreya</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Patel</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H10" t="str">
+        <v>IT</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="J10">
+        <v>75759</v>
+      </c>
+      <c r="K10">
+        <v>15151</v>
+      </c>
+      <c r="L10">
+        <v>7575</v>
+      </c>
+      <c r="M10">
+        <v>7059</v>
+      </c>
+      <c r="N10">
+        <v>105544</v>
+      </c>
+      <c r="O10">
+        <v>9091</v>
+      </c>
+      <c r="P10">
+        <v>10554</v>
+      </c>
+      <c r="Q10">
+        <v>85899</v>
+      </c>
+      <c r="T10">
+        <v>19</v>
+      </c>
+      <c r="U10" t="str">
+        <v>Nisha</v>
+      </c>
+      <c r="V10" t="str">
+        <v>Bose</v>
+      </c>
+      <c r="W10" t="str">
+        <v>Female</v>
+      </c>
+      <c r="X10" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="Y10" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="Z10">
+        <v>68167</v>
+      </c>
+      <c r="AA10">
+        <v>13633</v>
+      </c>
+      <c r="AB10">
+        <v>6816</v>
+      </c>
+      <c r="AC10">
+        <v>6534</v>
+      </c>
+      <c r="AD10">
+        <v>95150</v>
+      </c>
+      <c r="AE10">
+        <v>8180</v>
+      </c>
+      <c r="AF10">
+        <v>9515</v>
+      </c>
+      <c r="AG10">
+        <v>77455</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="D11">
+        <v>18</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Aarti</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Sharma</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H11" t="str">
+        <v>HR</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="J11">
+        <v>70505</v>
+      </c>
+      <c r="K11">
+        <v>14101</v>
+      </c>
+      <c r="L11">
+        <v>7050</v>
+      </c>
+      <c r="M11">
+        <v>3430</v>
+      </c>
+      <c r="N11">
+        <v>95086</v>
+      </c>
+      <c r="O11">
+        <v>8460</v>
+      </c>
+      <c r="P11">
+        <v>9508</v>
+      </c>
+      <c r="Q11">
+        <v>77118</v>
+      </c>
+      <c r="T11">
+        <v>21</v>
+      </c>
+      <c r="U11" t="str">
+        <v>Amit</v>
+      </c>
+      <c r="V11" t="str">
+        <v>Pillai</v>
+      </c>
+      <c r="W11" t="str">
+        <v>Male</v>
+      </c>
+      <c r="X11" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="Y11" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="Z11">
+        <v>79664</v>
+      </c>
+      <c r="AA11">
+        <v>15932</v>
+      </c>
+      <c r="AB11">
+        <v>7966</v>
+      </c>
+      <c r="AC11">
+        <v>8826</v>
+      </c>
+      <c r="AD11">
+        <v>112388</v>
+      </c>
+      <c r="AE11">
+        <v>9559</v>
+      </c>
+      <c r="AF11">
+        <v>11238</v>
+      </c>
+      <c r="AG11">
+        <v>91591</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="D12">
+        <v>19</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Nisha</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Bose</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="J12">
+        <v>68167</v>
+      </c>
+      <c r="K12">
+        <v>13633</v>
+      </c>
+      <c r="L12">
+        <v>6816</v>
+      </c>
+      <c r="M12">
+        <v>6534</v>
+      </c>
+      <c r="N12">
+        <v>95150</v>
+      </c>
+      <c r="O12">
+        <v>8180</v>
+      </c>
+      <c r="P12">
+        <v>9515</v>
+      </c>
+      <c r="Q12">
+        <v>77455</v>
+      </c>
+      <c r="T12">
+        <v>23</v>
+      </c>
+      <c r="U12" t="str">
+        <v>Pooja</v>
+      </c>
+      <c r="V12" t="str">
+        <v>Pillai</v>
+      </c>
+      <c r="W12" t="str">
+        <v>Female</v>
+      </c>
+      <c r="X12" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="Y12" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="Z12">
+        <v>67845</v>
+      </c>
+      <c r="AA12">
+        <v>13569</v>
+      </c>
+      <c r="AB12">
+        <v>6784</v>
+      </c>
+      <c r="AC12">
+        <v>5776</v>
+      </c>
+      <c r="AD12">
+        <v>93974</v>
+      </c>
+      <c r="AE12">
+        <v>8141</v>
+      </c>
+      <c r="AF12">
+        <v>9397</v>
+      </c>
+      <c r="AG12">
+        <v>76436</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="D13">
+        <v>22</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Rekha</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Iyer</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="J13">
+        <v>56954</v>
+      </c>
+      <c r="K13">
+        <v>11390</v>
+      </c>
+      <c r="L13">
+        <v>5695</v>
+      </c>
+      <c r="M13">
+        <v>3033</v>
+      </c>
+      <c r="N13">
+        <v>77072</v>
+      </c>
+      <c r="O13">
+        <v>6834</v>
+      </c>
+      <c r="P13">
+        <v>7707</v>
+      </c>
+      <c r="Q13">
+        <v>62531</v>
+      </c>
+      <c r="T13">
+        <v>34</v>
+      </c>
+      <c r="U13" t="str">
+        <v>Isha</v>
+      </c>
+      <c r="V13" t="str">
+        <v>Chatterjee</v>
+      </c>
+      <c r="W13" t="str">
+        <v>Female</v>
+      </c>
+      <c r="X13" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="Y13" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="Z13">
+        <v>49855</v>
+      </c>
+      <c r="AA13">
+        <v>9971</v>
+      </c>
+      <c r="AB13">
+        <v>4985</v>
+      </c>
+      <c r="AC13">
+        <v>3415</v>
+      </c>
+      <c r="AD13">
+        <v>68226</v>
+      </c>
+      <c r="AE13">
+        <v>5982</v>
+      </c>
+      <c r="AF13">
+        <v>6822</v>
+      </c>
+      <c r="AG13">
+        <v>55422</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="D14">
+        <v>23</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Pooja</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Pillai</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="J14">
+        <v>67845</v>
+      </c>
+      <c r="K14">
+        <v>13569</v>
+      </c>
+      <c r="L14">
+        <v>6784</v>
+      </c>
+      <c r="M14">
+        <v>5776</v>
+      </c>
+      <c r="N14">
+        <v>93974</v>
+      </c>
+      <c r="O14">
+        <v>8141</v>
+      </c>
+      <c r="P14">
+        <v>9397</v>
+      </c>
+      <c r="Q14">
+        <v>76436</v>
+      </c>
+      <c r="T14">
+        <v>36</v>
+      </c>
+      <c r="U14" t="str">
+        <v>Amit</v>
+      </c>
+      <c r="V14" t="str">
+        <v>Bose</v>
+      </c>
+      <c r="W14" t="str">
+        <v>Male</v>
+      </c>
+      <c r="X14" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="Y14" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="Z14">
+        <v>47876</v>
+      </c>
+      <c r="AA14">
+        <v>9575</v>
+      </c>
+      <c r="AB14">
+        <v>4787</v>
+      </c>
+      <c r="AC14">
+        <v>6335</v>
+      </c>
+      <c r="AD14">
+        <v>68573</v>
+      </c>
+      <c r="AE14">
+        <v>5745</v>
+      </c>
+      <c r="AF14">
+        <v>6857</v>
+      </c>
+      <c r="AG14">
+        <v>55971</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="D15">
+        <v>26</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Swati</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Bose</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H15" t="str">
+        <v>IT</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="J15">
+        <v>48968</v>
+      </c>
+      <c r="K15">
+        <v>9793</v>
+      </c>
+      <c r="L15">
+        <v>4896</v>
+      </c>
+      <c r="M15">
+        <v>8204</v>
+      </c>
+      <c r="N15">
+        <v>71861</v>
+      </c>
+      <c r="O15">
+        <v>5876</v>
+      </c>
+      <c r="P15">
+        <v>7186</v>
+      </c>
+      <c r="Q15">
+        <v>58799</v>
+      </c>
+      <c r="T15">
+        <v>39</v>
+      </c>
+      <c r="U15" t="str">
+        <v>Kavita</v>
+      </c>
+      <c r="V15" t="str">
+        <v>Desai</v>
+      </c>
+      <c r="W15" t="str">
+        <v>Female</v>
+      </c>
+      <c r="X15" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="Y15" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="Z15">
+        <v>50328</v>
+      </c>
+      <c r="AA15">
+        <v>10065</v>
+      </c>
+      <c r="AB15">
+        <v>5032</v>
+      </c>
+      <c r="AC15">
+        <v>6720</v>
+      </c>
+      <c r="AD15">
+        <v>72145</v>
+      </c>
+      <c r="AE15">
+        <v>6039</v>
+      </c>
+      <c r="AF15">
+        <v>7214</v>
+      </c>
+      <c r="AG15">
+        <v>58892</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="D16">
+        <v>32</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Priya</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Chatterjee</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H16" t="str">
+        <v>IT</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="J16">
+        <v>62716</v>
+      </c>
+      <c r="K16">
+        <v>12543</v>
+      </c>
+      <c r="L16">
+        <v>6271</v>
+      </c>
+      <c r="M16">
+        <v>6108</v>
+      </c>
+      <c r="N16">
+        <v>87638</v>
+      </c>
+      <c r="O16">
+        <v>7525</v>
+      </c>
+      <c r="P16">
+        <v>8763</v>
+      </c>
+      <c r="Q16">
+        <v>71350</v>
+      </c>
+      <c r="T16">
+        <v>55</v>
+      </c>
+      <c r="U16" t="str">
+        <v>Aarti</v>
+      </c>
+      <c r="V16" t="str">
+        <v>Nair</v>
+      </c>
+      <c r="W16" t="str">
+        <v>Female</v>
+      </c>
+      <c r="X16" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="Y16" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="Z16">
+        <v>20000</v>
+      </c>
+      <c r="AA16">
+        <v>4000</v>
+      </c>
+      <c r="AB16">
+        <v>2000</v>
+      </c>
+      <c r="AC16">
+        <v>3589</v>
+      </c>
+      <c r="AD16">
+        <v>29589</v>
+      </c>
+      <c r="AE16">
+        <v>2400</v>
+      </c>
+      <c r="AF16">
+        <v>2958</v>
+      </c>
+      <c r="AG16">
+        <v>24231</v>
+      </c>
+    </row>
+    <row r="17" spans="4:33" x14ac:dyDescent="0.3">
+      <c r="D17">
+        <v>34</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Isha</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Chatterjee</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="J17">
+        <v>49855</v>
+      </c>
+      <c r="K17">
+        <v>9971</v>
+      </c>
+      <c r="L17">
+        <v>4985</v>
+      </c>
+      <c r="M17">
+        <v>3415</v>
+      </c>
+      <c r="N17">
+        <v>68226</v>
+      </c>
+      <c r="O17">
+        <v>5982</v>
+      </c>
+      <c r="P17">
+        <v>6822</v>
+      </c>
+      <c r="Q17">
+        <v>55422</v>
+      </c>
+      <c r="T17">
+        <v>82</v>
+      </c>
+      <c r="U17" t="str">
+        <v>Akash</v>
+      </c>
+      <c r="V17" t="str">
+        <v>Joshi</v>
+      </c>
+      <c r="W17" t="str">
+        <v>Male</v>
+      </c>
+      <c r="X17" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="Y17" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="Z17">
+        <v>58807</v>
+      </c>
+      <c r="AA17">
+        <v>11761</v>
+      </c>
+      <c r="AB17">
+        <v>5880</v>
+      </c>
+      <c r="AC17">
+        <v>6518</v>
+      </c>
+      <c r="AD17">
+        <v>82966</v>
+      </c>
+      <c r="AE17">
+        <v>7056</v>
+      </c>
+      <c r="AF17">
+        <v>8296</v>
+      </c>
+      <c r="AG17">
+        <v>67614</v>
+      </c>
+    </row>
+    <row r="18" spans="4:33" x14ac:dyDescent="0.3">
+      <c r="D18">
+        <v>35</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Rashmi</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Naidu</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H18" t="str">
+        <v>HR</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="J18">
+        <v>44961</v>
+      </c>
+      <c r="K18">
+        <v>8992</v>
+      </c>
+      <c r="L18">
+        <v>4496</v>
+      </c>
+      <c r="M18">
+        <v>2327</v>
+      </c>
+      <c r="N18">
+        <v>60776</v>
+      </c>
+      <c r="O18">
+        <v>5395</v>
+      </c>
+      <c r="P18">
+        <v>6077</v>
+      </c>
+      <c r="Q18">
+        <v>49304</v>
+      </c>
+      <c r="T18">
+        <v>87</v>
+      </c>
+      <c r="U18" t="str">
+        <v>Yash</v>
+      </c>
+      <c r="V18" t="str">
+        <v>Reddy</v>
+      </c>
+      <c r="W18" t="str">
+        <v>Male</v>
+      </c>
+      <c r="X18" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="Y18" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="Z18">
+        <v>65347</v>
+      </c>
+      <c r="AA18">
+        <v>13069</v>
+      </c>
+      <c r="AB18">
+        <v>6534</v>
+      </c>
+      <c r="AC18">
+        <v>7333</v>
+      </c>
+      <c r="AD18">
+        <v>92283</v>
+      </c>
+      <c r="AE18">
+        <v>7841</v>
+      </c>
+      <c r="AF18">
+        <v>9228</v>
+      </c>
+      <c r="AG18">
+        <v>75214</v>
+      </c>
+    </row>
+    <row r="19" spans="4:33" x14ac:dyDescent="0.3">
+      <c r="D19">
+        <v>38</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Tanuja</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Desai</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="J19">
+        <v>20380</v>
+      </c>
+      <c r="K19">
+        <v>4076</v>
+      </c>
+      <c r="L19">
+        <v>2038</v>
+      </c>
+      <c r="M19">
+        <v>8075</v>
+      </c>
+      <c r="N19">
+        <v>34569</v>
+      </c>
+      <c r="O19">
+        <v>2445</v>
+      </c>
+      <c r="P19">
+        <v>3456</v>
+      </c>
+      <c r="Q19">
+        <v>28668</v>
+      </c>
+      <c r="T19">
+        <v>96</v>
+      </c>
+      <c r="U19" t="str">
+        <v>Priya</v>
+      </c>
+      <c r="V19" t="str">
+        <v>Joshi</v>
+      </c>
+      <c r="W19" t="str">
+        <v>Female</v>
+      </c>
+      <c r="X19" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="Y19" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="Z19">
+        <v>44954</v>
+      </c>
+      <c r="AA19">
+        <v>8990</v>
+      </c>
+      <c r="AB19">
+        <v>4495</v>
+      </c>
+      <c r="AC19">
+        <v>2259</v>
+      </c>
+      <c r="AD19">
+        <v>60698</v>
+      </c>
+      <c r="AE19">
+        <v>5394</v>
+      </c>
+      <c r="AF19">
+        <v>6069</v>
+      </c>
+      <c r="AG19">
+        <v>49235</v>
+      </c>
+    </row>
+    <row r="20" spans="4:33" x14ac:dyDescent="0.3">
+      <c r="D20">
+        <v>39</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Kavita</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Desai</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="J20">
+        <v>50328</v>
+      </c>
+      <c r="K20">
+        <v>10065</v>
+      </c>
+      <c r="L20">
+        <v>5032</v>
+      </c>
+      <c r="M20">
+        <v>6720</v>
+      </c>
+      <c r="N20">
+        <v>72145</v>
+      </c>
+      <c r="O20">
+        <v>6039</v>
+      </c>
+      <c r="P20">
+        <v>7214</v>
+      </c>
+      <c r="Q20">
+        <v>58892</v>
+      </c>
+      <c r="T20">
+        <v>100</v>
+      </c>
+      <c r="U20" t="str">
+        <v>Payal</v>
+      </c>
+      <c r="V20" t="str">
+        <v>Yadav</v>
+      </c>
+      <c r="W20" t="str">
+        <v>Female</v>
+      </c>
+      <c r="X20" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="Y20" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="Z20">
+        <v>54298</v>
+      </c>
+      <c r="AA20">
+        <v>10859</v>
+      </c>
+      <c r="AB20">
+        <v>5429</v>
+      </c>
+      <c r="AC20">
+        <v>9879</v>
+      </c>
+      <c r="AD20">
+        <v>80465</v>
+      </c>
+      <c r="AE20">
+        <v>6515</v>
+      </c>
+      <c r="AF20">
+        <v>8046</v>
+      </c>
+      <c r="AG20">
+        <v>65904</v>
+      </c>
+    </row>
+    <row r="21" spans="4:33" x14ac:dyDescent="0.3">
+      <c r="D21">
+        <v>43</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Anjali</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Singh</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="J21">
+        <v>40221</v>
+      </c>
+      <c r="K21">
+        <v>8044</v>
+      </c>
+      <c r="L21">
+        <v>4022</v>
+      </c>
+      <c r="M21">
+        <v>6861</v>
+      </c>
+      <c r="N21">
+        <v>59148</v>
+      </c>
+      <c r="O21">
+        <v>4826</v>
+      </c>
+      <c r="P21">
+        <v>5914</v>
+      </c>
+      <c r="Q21">
+        <v>48408</v>
+      </c>
+    </row>
+    <row r="22" spans="4:33" x14ac:dyDescent="0.3">
+      <c r="D22">
+        <v>44</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Priya</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Singh</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="J22">
+        <v>62114</v>
+      </c>
+      <c r="K22">
+        <v>12422</v>
+      </c>
+      <c r="L22">
+        <v>6211</v>
+      </c>
+      <c r="M22">
+        <v>8503</v>
+      </c>
+      <c r="N22">
+        <v>89250</v>
+      </c>
+      <c r="O22">
+        <v>7453</v>
+      </c>
+      <c r="P22">
+        <v>8925</v>
+      </c>
+      <c r="Q22">
+        <v>72872</v>
+      </c>
+    </row>
+    <row r="23" spans="4:33" x14ac:dyDescent="0.3">
+      <c r="D23">
+        <v>46</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Shreya</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Desai</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="I23" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="J23">
+        <v>51805</v>
+      </c>
+      <c r="K23">
+        <v>10361</v>
+      </c>
+      <c r="L23">
+        <v>5180</v>
+      </c>
+      <c r="M23">
+        <v>8670</v>
+      </c>
+      <c r="N23">
+        <v>76016</v>
+      </c>
+      <c r="O23">
+        <v>6216</v>
+      </c>
+      <c r="P23">
+        <v>7601</v>
+      </c>
+      <c r="Q23">
+        <v>62199</v>
+      </c>
+    </row>
+    <row r="24" spans="4:33" x14ac:dyDescent="0.3">
+      <c r="D24">
+        <v>48</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Shreya</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Joshi</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="I24" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="J24">
+        <v>59008</v>
+      </c>
+      <c r="K24">
+        <v>11801</v>
+      </c>
+      <c r="L24">
+        <v>5900</v>
+      </c>
+      <c r="M24">
+        <v>4141</v>
+      </c>
+      <c r="N24">
+        <v>80850</v>
+      </c>
+      <c r="O24">
+        <v>7080</v>
+      </c>
+      <c r="P24">
+        <v>8085</v>
+      </c>
+      <c r="Q24">
+        <v>65685</v>
+      </c>
+    </row>
+    <row r="25" spans="4:33" x14ac:dyDescent="0.3">
+      <c r="D25">
+        <v>50</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Tanuja</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Bose</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="I25" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="J25">
+        <v>60843</v>
+      </c>
+      <c r="K25">
+        <v>12168</v>
+      </c>
+      <c r="L25">
+        <v>6084</v>
+      </c>
+      <c r="M25">
+        <v>4747</v>
+      </c>
+      <c r="N25">
+        <v>83842</v>
+      </c>
+      <c r="O25">
+        <v>7301</v>
+      </c>
+      <c r="P25">
+        <v>8384</v>
+      </c>
+      <c r="Q25">
+        <v>68157</v>
+      </c>
+    </row>
+    <row r="26" spans="4:33" x14ac:dyDescent="0.3">
+      <c r="D26">
+        <v>51</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Komal</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Kumar</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="I26" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="J26">
+        <v>24916</v>
+      </c>
+      <c r="K26">
+        <v>4983</v>
+      </c>
+      <c r="L26">
+        <v>2491</v>
+      </c>
+      <c r="M26">
+        <v>7396</v>
+      </c>
+      <c r="N26">
+        <v>39786</v>
+      </c>
+      <c r="O26">
+        <v>2989</v>
+      </c>
+      <c r="P26">
+        <v>3978</v>
+      </c>
+      <c r="Q26">
+        <v>32819</v>
+      </c>
+    </row>
+    <row r="27" spans="4:33" x14ac:dyDescent="0.3">
+      <c r="D27">
+        <v>53</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Meena</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Mehta</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="J27">
+        <v>35096</v>
+      </c>
+      <c r="K27">
+        <v>7019</v>
+      </c>
+      <c r="L27">
+        <v>3509</v>
+      </c>
+      <c r="M27">
+        <v>8514</v>
+      </c>
+      <c r="N27">
+        <v>54138</v>
+      </c>
+      <c r="O27">
+        <v>4211</v>
+      </c>
+      <c r="P27">
+        <v>5413</v>
+      </c>
+      <c r="Q27">
+        <v>44514</v>
+      </c>
+    </row>
+    <row r="28" spans="4:33" x14ac:dyDescent="0.3">
+      <c r="D28">
+        <v>55</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Aarti</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Nair</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="J28">
+        <v>20000</v>
+      </c>
+      <c r="K28">
+        <v>4000</v>
+      </c>
+      <c r="L28">
+        <v>2000</v>
+      </c>
+      <c r="M28">
+        <v>3589</v>
+      </c>
+      <c r="N28">
+        <v>29589</v>
+      </c>
+      <c r="O28">
+        <v>2400</v>
+      </c>
+      <c r="P28">
+        <v>2958</v>
+      </c>
+      <c r="Q28">
+        <v>24231</v>
+      </c>
+    </row>
+    <row r="29" spans="4:33" x14ac:dyDescent="0.3">
+      <c r="D29">
+        <v>56</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Kavita</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Sharma</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="J29">
+        <v>53126</v>
+      </c>
+      <c r="K29">
+        <v>10625</v>
+      </c>
+      <c r="L29">
+        <v>5312</v>
+      </c>
+      <c r="M29">
+        <v>6479</v>
+      </c>
+      <c r="N29">
+        <v>75542</v>
+      </c>
+      <c r="O29">
+        <v>6375</v>
+      </c>
+      <c r="P29">
+        <v>7554</v>
+      </c>
+      <c r="Q29">
+        <v>61613</v>
+      </c>
+    </row>
+    <row r="30" spans="4:33" x14ac:dyDescent="0.3">
+      <c r="D30">
+        <v>57</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Rekha</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Verma</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="I30" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="J30">
+        <v>77187</v>
+      </c>
+      <c r="K30">
+        <v>15437</v>
+      </c>
+      <c r="L30">
+        <v>7718</v>
+      </c>
+      <c r="M30">
+        <v>9513</v>
+      </c>
+      <c r="N30">
+        <v>109855</v>
+      </c>
+      <c r="O30">
+        <v>9262</v>
+      </c>
+      <c r="P30">
+        <v>10985</v>
+      </c>
+      <c r="Q30">
+        <v>89608</v>
+      </c>
+    </row>
+    <row r="31" spans="4:33" x14ac:dyDescent="0.3">
+      <c r="D31">
+        <v>58</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Sunita</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Verma</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="J31">
+        <v>64622</v>
+      </c>
+      <c r="K31">
+        <v>12924</v>
+      </c>
+      <c r="L31">
+        <v>6462</v>
+      </c>
+      <c r="M31">
+        <v>3308</v>
+      </c>
+      <c r="N31">
+        <v>87316</v>
+      </c>
+      <c r="O31">
+        <v>7754</v>
+      </c>
+      <c r="P31">
+        <v>8731</v>
+      </c>
+      <c r="Q31">
+        <v>70831</v>
+      </c>
+    </row>
+    <row r="32" spans="4:33" x14ac:dyDescent="0.3">
+      <c r="D32">
+        <v>59</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Aarti</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Naidu</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H32" t="str">
+        <v>IT</v>
+      </c>
+      <c r="I32" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="J32">
+        <v>25787</v>
+      </c>
+      <c r="K32">
+        <v>5157</v>
+      </c>
+      <c r="L32">
+        <v>2578</v>
+      </c>
+      <c r="M32">
+        <v>4235</v>
+      </c>
+      <c r="N32">
+        <v>37757</v>
+      </c>
+      <c r="O32">
+        <v>3094</v>
+      </c>
+      <c r="P32">
+        <v>3775</v>
+      </c>
+      <c r="Q32">
+        <v>30888</v>
+      </c>
+    </row>
+    <row r="33" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D33">
+        <v>61</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Aarti</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Patel</v>
+      </c>
+      <c r="G33" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H33" t="str">
+        <v>HR</v>
+      </c>
+      <c r="I33" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="J33">
+        <v>34491</v>
+      </c>
+      <c r="K33">
+        <v>6898</v>
+      </c>
+      <c r="L33">
+        <v>3449</v>
+      </c>
+      <c r="M33">
+        <v>7675</v>
+      </c>
+      <c r="N33">
+        <v>52513</v>
+      </c>
+      <c r="O33">
+        <v>4138</v>
+      </c>
+      <c r="P33">
+        <v>5251</v>
+      </c>
+      <c r="Q33">
+        <v>43124</v>
+      </c>
+    </row>
+    <row r="34" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D34">
+        <v>63</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Pooja</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Chatterjee</v>
+      </c>
+      <c r="G34" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H34" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="I34" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="J34">
+        <v>66958</v>
+      </c>
+      <c r="K34">
+        <v>13391</v>
+      </c>
+      <c r="L34">
+        <v>6695</v>
+      </c>
+      <c r="M34">
+        <v>9327</v>
+      </c>
+      <c r="N34">
+        <v>96371</v>
+      </c>
+      <c r="O34">
+        <v>8034</v>
+      </c>
+      <c r="P34">
+        <v>9637</v>
+      </c>
+      <c r="Q34">
+        <v>78700</v>
+      </c>
+    </row>
+    <row r="35" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D35">
+        <v>64</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Swati</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Reddy</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H35" t="str">
+        <v>HR</v>
+      </c>
+      <c r="I35" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="J35">
+        <v>21661</v>
+      </c>
+      <c r="K35">
+        <v>4332</v>
+      </c>
+      <c r="L35">
+        <v>2166</v>
+      </c>
+      <c r="M35">
+        <v>2432</v>
+      </c>
+      <c r="N35">
+        <v>30591</v>
+      </c>
+      <c r="O35">
+        <v>2599</v>
+      </c>
+      <c r="P35">
+        <v>3059</v>
+      </c>
+      <c r="Q35">
+        <v>24933</v>
+      </c>
+    </row>
+    <row r="36" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D36">
+        <v>65</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Isha</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Nair</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H36" t="str">
+        <v>HR</v>
+      </c>
+      <c r="I36" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="J36">
+        <v>29391</v>
+      </c>
+      <c r="K36">
+        <v>5878</v>
+      </c>
+      <c r="L36">
+        <v>2939</v>
+      </c>
+      <c r="M36">
+        <v>9277</v>
+      </c>
+      <c r="N36">
+        <v>47485</v>
+      </c>
+      <c r="O36">
+        <v>3526</v>
+      </c>
+      <c r="P36">
+        <v>4748</v>
+      </c>
+      <c r="Q36">
+        <v>39211</v>
+      </c>
+    </row>
+    <row r="37" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D37">
+        <v>68</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Isha</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Naidu</v>
+      </c>
+      <c r="G37" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H37" t="str">
+        <v>IT</v>
+      </c>
+      <c r="I37" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="J37">
+        <v>24203</v>
+      </c>
+      <c r="K37">
+        <v>4840</v>
+      </c>
+      <c r="L37">
+        <v>2420</v>
+      </c>
+      <c r="M37">
+        <v>9173</v>
+      </c>
+      <c r="N37">
+        <v>40636</v>
+      </c>
+      <c r="O37">
+        <v>2904</v>
+      </c>
+      <c r="P37">
+        <v>4063</v>
+      </c>
+      <c r="Q37">
+        <v>33669</v>
+      </c>
+    </row>
+    <row r="38" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D38">
+        <v>70</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Sunita</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Kumar</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H38" t="str">
+        <v>HR</v>
+      </c>
+      <c r="I38" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="J38">
+        <v>72192</v>
+      </c>
+      <c r="K38">
+        <v>14438</v>
+      </c>
+      <c r="L38">
+        <v>7219</v>
+      </c>
+      <c r="M38">
+        <v>6505</v>
+      </c>
+      <c r="N38">
+        <v>100354</v>
+      </c>
+      <c r="O38">
+        <v>8663</v>
+      </c>
+      <c r="P38">
+        <v>10035</v>
+      </c>
+      <c r="Q38">
+        <v>81656</v>
+      </c>
+    </row>
+    <row r="39" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D39">
+        <v>71</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Pooja</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Mishra</v>
+      </c>
+      <c r="G39" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H39" t="str">
+        <v>HR</v>
+      </c>
+      <c r="I39" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="J39">
+        <v>25713</v>
+      </c>
+      <c r="K39">
+        <v>5142</v>
+      </c>
+      <c r="L39">
+        <v>2571</v>
+      </c>
+      <c r="M39">
+        <v>7926</v>
+      </c>
+      <c r="N39">
+        <v>41352</v>
+      </c>
+      <c r="O39">
+        <v>3085</v>
+      </c>
+      <c r="P39">
+        <v>4135</v>
+      </c>
+      <c r="Q39">
+        <v>34132</v>
+      </c>
+    </row>
+    <row r="40" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D40">
+        <v>72</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Divya</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Bose</v>
+      </c>
+      <c r="G40" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H40" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="I40" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="J40">
+        <v>54929</v>
+      </c>
+      <c r="K40">
+        <v>10985</v>
+      </c>
+      <c r="L40">
+        <v>5492</v>
+      </c>
+      <c r="M40">
+        <v>4242</v>
+      </c>
+      <c r="N40">
+        <v>75648</v>
+      </c>
+      <c r="O40">
+        <v>6591</v>
+      </c>
+      <c r="P40">
+        <v>7564</v>
+      </c>
+      <c r="Q40">
+        <v>61493</v>
+      </c>
+    </row>
+    <row r="41" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D41">
+        <v>75</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Isha</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Sharma</v>
+      </c>
+      <c r="G41" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H41" t="str">
+        <v>HR</v>
+      </c>
+      <c r="I41" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="J41">
+        <v>77565</v>
+      </c>
+      <c r="K41">
+        <v>15513</v>
+      </c>
+      <c r="L41">
+        <v>7756</v>
+      </c>
+      <c r="M41">
+        <v>8360</v>
+      </c>
+      <c r="N41">
+        <v>109194</v>
+      </c>
+      <c r="O41">
+        <v>9307</v>
+      </c>
+      <c r="P41">
+        <v>10919</v>
+      </c>
+      <c r="Q41">
+        <v>88968</v>
+      </c>
+    </row>
+    <row r="42" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D42">
+        <v>80</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Komal</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Sharma</v>
+      </c>
+      <c r="G42" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H42" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="I42" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="J42">
+        <v>44871</v>
+      </c>
+      <c r="K42">
+        <v>8974</v>
+      </c>
+      <c r="L42">
+        <v>4487</v>
+      </c>
+      <c r="M42">
+        <v>3543</v>
+      </c>
+      <c r="N42">
+        <v>61875</v>
+      </c>
+      <c r="O42">
+        <v>5384</v>
+      </c>
+      <c r="P42">
+        <v>6187</v>
+      </c>
+      <c r="Q42">
+        <v>50304</v>
+      </c>
+    </row>
+    <row r="43" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D43">
+        <v>81</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Priya</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Gupta</v>
+      </c>
+      <c r="G43" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H43" t="str">
+        <v>IT</v>
+      </c>
+      <c r="I43" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="J43">
+        <v>37428</v>
+      </c>
+      <c r="K43">
+        <v>7485</v>
+      </c>
+      <c r="L43">
+        <v>3742</v>
+      </c>
+      <c r="M43">
+        <v>8568</v>
+      </c>
+      <c r="N43">
+        <v>57223</v>
+      </c>
+      <c r="O43">
+        <v>4491</v>
+      </c>
+      <c r="P43">
+        <v>5722</v>
+      </c>
+      <c r="Q43">
+        <v>47010</v>
+      </c>
+    </row>
+    <row r="44" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D44">
+        <v>86</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Payal</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Joshi</v>
+      </c>
+      <c r="G44" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H44" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="I44" t="str">
+        <v>Executive</v>
+      </c>
+      <c r="J44">
+        <v>50437</v>
+      </c>
+      <c r="K44">
+        <v>10087</v>
+      </c>
+      <c r="L44">
+        <v>5043</v>
+      </c>
+      <c r="M44">
+        <v>5150</v>
+      </c>
+      <c r="N44">
+        <v>70717</v>
+      </c>
+      <c r="O44">
+        <v>6052</v>
+      </c>
+      <c r="P44">
+        <v>7071</v>
+      </c>
+      <c r="Q44">
+        <v>57594</v>
+      </c>
+    </row>
+    <row r="45" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D45">
+        <v>88</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Pooja</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Nair</v>
+      </c>
+      <c r="G45" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H45" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="I45" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="J45">
+        <v>57201</v>
+      </c>
+      <c r="K45">
+        <v>11440</v>
+      </c>
+      <c r="L45">
+        <v>5720</v>
+      </c>
+      <c r="M45">
+        <v>8967</v>
+      </c>
+      <c r="N45">
+        <v>83328</v>
+      </c>
+      <c r="O45">
+        <v>6864</v>
+      </c>
+      <c r="P45">
+        <v>8332</v>
+      </c>
+      <c r="Q45">
+        <v>68132</v>
+      </c>
+    </row>
+    <row r="46" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D46">
+        <v>89</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Nisha</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Desai</v>
+      </c>
+      <c r="G46" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H46" t="str">
+        <v>IT</v>
+      </c>
+      <c r="I46" t="str">
+        <v>Lead</v>
+      </c>
+      <c r="J46">
+        <v>23348</v>
+      </c>
+      <c r="K46">
+        <v>4669</v>
+      </c>
+      <c r="L46">
+        <v>2334</v>
+      </c>
+      <c r="M46">
+        <v>9674</v>
+      </c>
+      <c r="N46">
+        <v>40025</v>
+      </c>
+      <c r="O46">
+        <v>2801</v>
+      </c>
+      <c r="P46">
+        <v>4002</v>
+      </c>
+      <c r="Q46">
+        <v>33222</v>
+      </c>
+    </row>
+    <row r="47" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D47">
+        <v>91</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Neha</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Chatterjee</v>
+      </c>
+      <c r="G47" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H47" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="I47" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="J47">
+        <v>59553</v>
+      </c>
+      <c r="K47">
+        <v>11910</v>
+      </c>
+      <c r="L47">
+        <v>5955</v>
+      </c>
+      <c r="M47">
+        <v>5930</v>
+      </c>
+      <c r="N47">
+        <v>83348</v>
+      </c>
+      <c r="O47">
+        <v>7146</v>
+      </c>
+      <c r="P47">
+        <v>8334</v>
+      </c>
+      <c r="Q47">
+        <v>67868</v>
+      </c>
+    </row>
+    <row r="48" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D48">
+        <v>92</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Isha</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Joshi</v>
+      </c>
+      <c r="G48" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H48" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="I48" t="str">
+        <v>Senior Executive</v>
+      </c>
+      <c r="J48">
+        <v>49760</v>
+      </c>
+      <c r="K48">
+        <v>9952</v>
+      </c>
+      <c r="L48">
+        <v>4976</v>
+      </c>
+      <c r="M48">
+        <v>8137</v>
+      </c>
+      <c r="N48">
+        <v>72825</v>
+      </c>
+      <c r="O48">
+        <v>5971</v>
+      </c>
+      <c r="P48">
+        <v>7282</v>
+      </c>
+      <c r="Q48">
+        <v>59572</v>
+      </c>
+    </row>
+    <row r="49" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D49">
+        <v>95</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Isha</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Singh</v>
+      </c>
+      <c r="G49" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H49" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="I49" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="J49">
+        <v>66819</v>
+      </c>
+      <c r="K49">
+        <v>13363</v>
+      </c>
+      <c r="L49">
+        <v>6681</v>
+      </c>
+      <c r="M49">
+        <v>5844</v>
+      </c>
+      <c r="N49">
+        <v>92707</v>
+      </c>
+      <c r="O49">
+        <v>8018</v>
+      </c>
+      <c r="P49">
+        <v>9270</v>
+      </c>
+      <c r="Q49">
+        <v>75419</v>
+      </c>
+    </row>
+    <row r="50" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D50">
+        <v>96</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Priya</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Joshi</v>
+      </c>
+      <c r="G50" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H50" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="I50" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="J50">
+        <v>44954</v>
+      </c>
+      <c r="K50">
+        <v>8990</v>
+      </c>
+      <c r="L50">
+        <v>4495</v>
+      </c>
+      <c r="M50">
+        <v>2259</v>
+      </c>
+      <c r="N50">
+        <v>60698</v>
+      </c>
+      <c r="O50">
+        <v>5394</v>
+      </c>
+      <c r="P50">
+        <v>6069</v>
+      </c>
+      <c r="Q50">
+        <v>49235</v>
+      </c>
+    </row>
+    <row r="51" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D51">
+        <v>97</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Payal</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Naidu</v>
+      </c>
+      <c r="G51" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H51" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="I51" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="J51">
+        <v>73201</v>
+      </c>
+      <c r="K51">
+        <v>14640</v>
+      </c>
+      <c r="L51">
+        <v>7320</v>
+      </c>
+      <c r="M51">
+        <v>9948</v>
+      </c>
+      <c r="N51">
+        <v>105109</v>
+      </c>
+      <c r="O51">
+        <v>8784</v>
+      </c>
+      <c r="P51">
+        <v>10510</v>
+      </c>
+      <c r="Q51">
+        <v>85815</v>
+      </c>
+    </row>
+    <row r="52" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D52">
+        <v>100</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Payal</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Yadav</v>
+      </c>
+      <c r="G52" t="str">
+        <v>Female</v>
+      </c>
+      <c r="H52" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="I52" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="J52">
+        <v>54298</v>
+      </c>
+      <c r="K52">
+        <v>10859</v>
+      </c>
+      <c r="L52">
+        <v>5429</v>
+      </c>
+      <c r="M52">
+        <v>9879</v>
+      </c>
+      <c r="N52">
+        <v>80465</v>
+      </c>
+      <c r="O52">
+        <v>6515</v>
+      </c>
+      <c r="P52">
+        <v>8046</v>
+      </c>
+      <c r="Q52">
+        <v>65904</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4EDC0C25-FBCB-43C9-B089-F601223FCF37}">
+          <x14:formula1>
+            <xm:f>'Employee Data'!$D$2:$D$101</xm:f>
+          </x14:formula1>
+          <xm:sqref>B3</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" xr:uid="{9708CB7F-A8E9-499B-B46A-5595181A5595}">
+          <x14:formula1>
+            <xm:f>'Employee Data'!$E$2:$E$101</xm:f>
+          </x14:formula1>
+          <xm:sqref>B4</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
 </file>